--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_45.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3800552.466651631</v>
+        <v>3801656.990167139</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6591.459428701596</v>
+        <v>6591.459428699045</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6591.459428701596</v>
+        <v>6591.459428699045</v>
       </c>
     </row>
     <row r="11">
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>5.296708396048877</v>
+        <v>3.343301935257416</v>
       </c>
       <c r="H2" t="n">
-        <v>3.769060713577687</v>
+        <v>3.769060713577661</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.41253966161941</v>
+        <v>87.36594612241251</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8629887637397</v>
+        <v>184.8629887637398</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1881709204699</v>
+        <v>249.18817092047</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>115.9227665017098</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>86.01413451627722</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -781,25 +781,25 @@
         <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.5184388018132</v>
+        <v>133.5184388018133</v>
       </c>
       <c r="S3" t="n">
         <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>4.464774651476091</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1957842884886345</v>
       </c>
       <c r="V3" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>374</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.51638189435317</v>
+        <v>91.51638189435316</v>
       </c>
       <c r="N4" t="n">
         <v>142.7621408454554</v>
@@ -854,7 +854,7 @@
         <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>264.9837661807364</v>
+        <v>264.9837661807365</v>
       </c>
       <c r="Q4" t="n">
         <v>310.286266425598</v>
@@ -909,10 +909,10 @@
         <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>5.722467174369123</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.953406460792978</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -973,22 +973,22 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>153.6008523136666</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>317.3060129582571</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
         <v>133.5184388018132</v>
@@ -1027,7 +1027,7 @@
         <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1957842884886531</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1149,7 +1149,7 @@
         <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>1.953406460791434</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.41253966161941</v>
+        <v>87.36594612241251</v>
       </c>
       <c r="T8" t="n">
         <v>184.8629887637397</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125.5209519236642</v>
+        <v>310.9106550128582</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1225,10 +1225,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0284079411381</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="Y9" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
     </row>
     <row r="10">
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>142.0601778525742</v>
+        <v>139.1041209967842</v>
       </c>
       <c r="T11" t="n">
         <v>259.5690792160011</v>
@@ -1428,7 +1428,7 @@
         <v>308.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>314.4174191251558</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>271.2818334606677</v>
@@ -1447,7 +1447,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
         <v>26.93768689770263</v>
@@ -1459,13 +1459,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>324.9931585165368</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H12" t="n">
-        <v>3.959653224156966</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I12" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>179.932929367851</v>
       </c>
       <c r="S12" t="n">
-        <v>131.7003678891396</v>
+        <v>314.8596346682833</v>
       </c>
       <c r="T12" t="n">
         <v>81.34934068921194</v>
@@ -1507,7 +1507,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>424.1036653070577</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>419.8627394453875</v>
@@ -1620,7 +1620,7 @@
         <v>81.36239741264433</v>
       </c>
       <c r="H14" t="n">
-        <v>72.7233722713666</v>
+        <v>69.767315415597</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>139.1041209967824</v>
+        <v>142.0601778525742</v>
       </c>
       <c r="T14" t="n">
         <v>259.5690792160011</v>
@@ -1687,19 +1687,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>3.993158516536766</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H15" t="n">
-        <v>3.959653224156966</v>
+        <v>109.3140700071608</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R15" t="n">
         <v>179.932929367851</v>
@@ -1741,16 +1741,16 @@
         <v>79.16125598660182</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>261.550659545278</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>158.0432560997829</v>
+        <v>158.0432560997847</v>
       </c>
       <c r="C17" t="n">
         <v>128.4745782429939</v>
@@ -1921,13 +1921,13 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
         <v>18.63624233787687</v>
@@ -1936,7 +1936,7 @@
         <v>3.993158516536766</v>
       </c>
       <c r="H18" t="n">
-        <v>3.959653224156966</v>
+        <v>187.1189200033006</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1975,16 +1975,16 @@
         <v>81.34934068921194</v>
       </c>
       <c r="U18" t="n">
-        <v>400.1612559866018</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V18" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>282.0220062245313</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
         <v>78.39139276613435</v>
@@ -2094,7 +2094,7 @@
         <v>81.36239741264436</v>
       </c>
       <c r="H20" t="n">
-        <v>69.76731541559633</v>
+        <v>69.7673154156098</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2203,25 +2203,25 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R21" t="n">
-        <v>500.932929367851</v>
+        <v>179.932929367851</v>
       </c>
       <c r="S21" t="n">
         <v>131.7003678891396</v>
       </c>
       <c r="T21" t="n">
-        <v>402.3493406892119</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U21" t="n">
         <v>400.1612559866018</v>
       </c>
       <c r="V21" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>216.7275596928324</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>98.86273944538755</v>
+        <v>204.2171562283914</v>
       </c>
       <c r="Y21" t="n">
         <v>78.39139276613435</v>
@@ -2328,7 +2328,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.36239741264433</v>
+        <v>78.40634055685446</v>
       </c>
       <c r="H23" t="n">
         <v>72.7233722713666</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>139.1041209967824</v>
+        <v>142.0601778525742</v>
       </c>
       <c r="T23" t="n">
         <v>259.5690792160011</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>179.932929367851</v>
@@ -2449,16 +2449,16 @@
         <v>81.34934068921194</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1612559866018</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V24" t="n">
-        <v>93.51066719152016</v>
+        <v>276.6699339706637</v>
       </c>
       <c r="W24" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>204.2171562283915</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y24" t="n">
         <v>399.3913927661343</v>
@@ -2565,10 +2565,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.36239741264436</v>
+        <v>81.36239741264433</v>
       </c>
       <c r="H26" t="n">
-        <v>72.72337227136661</v>
+        <v>73.64811541557496</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>142.0601778525742</v>
@@ -2607,7 +2607,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U26" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.55655664632661</v>
+        <v>168.9109734293304</v>
       </c>
       <c r="C27" t="n">
         <v>40.09991244551929</v>
@@ -2644,10 +2644,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>324.9931585165368</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H27" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2683,16 +2683,16 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T27" t="n">
-        <v>186.7037574722156</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16125598660184</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>419.8627394453875</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M28" t="n">
         <v>101.5443818943532</v>
@@ -2747,19 +2747,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O28" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P28" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q28" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R28" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S28" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>246.7158234254702</v>
       </c>
       <c r="C30" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
@@ -2878,13 +2878,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>3.993158516536777</v>
       </c>
       <c r="H30" t="n">
-        <v>187.1189200033006</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
         <v>78.39139276613435</v>
@@ -3039,10 +3039,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.36239741264436</v>
+        <v>81.36239741264433</v>
       </c>
       <c r="H32" t="n">
-        <v>72.72337227136661</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U32" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3106,22 +3106,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.993158516536777</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H33" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3157,19 +3157,19 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T33" t="n">
-        <v>81.34934068921193</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16125598660184</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V33" t="n">
-        <v>93.51066719152016</v>
+        <v>276.6699339706637</v>
       </c>
       <c r="W33" t="n">
-        <v>294.532409688972</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>399.3913927661343</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M34" t="n">
         <v>101.5443818943532</v>
@@ -3221,19 +3221,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O34" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P34" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q34" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R34" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S34" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>132.4136560997828</v>
+        <v>136.9993129555745</v>
       </c>
       <c r="C35" t="n">
         <v>104.4745782429939</v>
@@ -3276,7 +3276,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>57.36239741264433</v>
+        <v>52.77674055685252</v>
       </c>
       <c r="H35" t="n">
         <v>48.7233722713666</v>
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>271.7085228072759</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>16.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>155.932929367851</v>
       </c>
       <c r="S36" t="n">
-        <v>107.7003678891396</v>
+        <v>183.9531756539885</v>
       </c>
       <c r="T36" t="n">
         <v>57.34934068921194</v>
@@ -3406,10 +3406,10 @@
         <v>87.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>74.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>54.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3516,7 +3516,7 @@
         <v>57.36239741264435</v>
       </c>
       <c r="H38" t="n">
-        <v>48.72337227136661</v>
+        <v>44.13771541563285</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>113.4745209968696</v>
+        <v>118.0601778525742</v>
       </c>
       <c r="T38" t="n">
         <v>235.5690792160011</v>
@@ -3583,13 +3583,13 @@
         <v>16.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>2.937686897702633</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>76.25280776485252</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>155.932929367851</v>
@@ -3634,13 +3634,13 @@
         <v>57.34934068921193</v>
       </c>
       <c r="U39" t="n">
-        <v>400.1612559866018</v>
+        <v>55.16125598660184</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>432.3731429098285</v>
+        <v>171.3176111148734</v>
       </c>
       <c r="X39" t="n">
         <v>419.8627394453875</v>
@@ -3750,10 +3750,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>52.7767405568525</v>
+        <v>57.36239741264433</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72337227136661</v>
+        <v>44.1377154155748</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>235.5690792160011</v>
       </c>
       <c r="U41" t="n">
-        <v>304.1096985586609</v>
+        <v>304.109698558661</v>
       </c>
       <c r="V41" t="n">
         <v>284.8510241668239</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>39.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>16.09991244551929</v>
@@ -3829,13 +3829,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>324.9931585165368</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>18.45479925218331</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,31 +3859,31 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>77.80484999613995</v>
+        <v>76.25280776484172</v>
       </c>
       <c r="R42" t="n">
         <v>155.932929367851</v>
       </c>
       <c r="S42" t="n">
-        <v>452.7003678891396</v>
+        <v>107.7003678891396</v>
       </c>
       <c r="T42" t="n">
-        <v>57.34934068921193</v>
+        <v>57.34934068921194</v>
       </c>
       <c r="U42" t="n">
-        <v>400.1612559866018</v>
+        <v>55.16125598660182</v>
       </c>
       <c r="V42" t="n">
         <v>69.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>87.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>54.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -3926,25 +3926,25 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>77.54438189435318</v>
+        <v>77.54438189435319</v>
       </c>
       <c r="N43" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O43" t="n">
-        <v>207.0003837511461</v>
+        <v>207.000383751146</v>
       </c>
       <c r="P43" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q43" t="n">
-        <v>328.442266425598</v>
+        <v>328.4422664255979</v>
       </c>
       <c r="R43" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S43" t="n">
-        <v>6.468578063511176</v>
+        <v>6.468578063511188</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>57.36239741264435</v>
+        <v>52.7767405568525</v>
       </c>
       <c r="H44" t="n">
         <v>48.72337227136661</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>113.4745209967827</v>
+        <v>118.0601778525742</v>
       </c>
       <c r="T44" t="n">
         <v>235.5690792160011</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>76.25280776477643</v>
       </c>
       <c r="R45" t="n">
         <v>500.932929367851</v>
@@ -4108,19 +4108,19 @@
         <v>57.34934068921193</v>
       </c>
       <c r="U45" t="n">
-        <v>284.9853193694638</v>
+        <v>55.16125598660184</v>
       </c>
       <c r="V45" t="n">
-        <v>69.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>87.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>399.3913927661343</v>
+        <v>54.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.8416377852028</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>58.86731632763319</v>
+        <v>56.8941784884499</v>
       </c>
       <c r="D2" t="n">
-        <v>48.42372467121926</v>
+        <v>46.45058683203597</v>
       </c>
       <c r="E2" t="n">
-        <v>44.016361431958</v>
+        <v>42.04322359277471</v>
       </c>
       <c r="F2" t="n">
-        <v>39.07734253497633</v>
+        <v>37.10420469579304</v>
       </c>
       <c r="G2" t="n">
         <v>33.72713203391686</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="J2" t="n">
-        <v>30.01969029977264</v>
+        <v>30.01969029977267</v>
       </c>
       <c r="K2" t="n">
-        <v>82.16427879223495</v>
+        <v>261.865820646305</v>
       </c>
       <c r="L2" t="n">
-        <v>326.5557936111288</v>
+        <v>326.5557936111291</v>
       </c>
       <c r="M2" t="n">
-        <v>696.8157936111288</v>
+        <v>696.8157936111295</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.075793611129</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.075793611129</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1125.740000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.724707412506</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.994415731961</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U2" t="n">
-        <v>971.2891925799706</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V2" t="n">
-        <v>739.1164408963101</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W2" t="n">
-        <v>498.3351520266661</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X2" t="n">
-        <v>304.1110778239714</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.6692266292175</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>241.7346173614335</v>
+        <v>328.6175815192909</v>
       </c>
       <c r="C3" t="n">
-        <v>241.7346173614335</v>
+        <v>241.7346173614351</v>
       </c>
       <c r="D3" t="n">
-        <v>241.7346173614335</v>
+        <v>241.7346173614351</v>
       </c>
       <c r="E3" t="n">
-        <v>241.7346173614335</v>
+        <v>241.7346173614351</v>
       </c>
       <c r="F3" t="n">
-        <v>241.7346173614335</v>
+        <v>241.7346173614351</v>
       </c>
       <c r="G3" t="n">
-        <v>241.7346173614335</v>
+        <v>241.7346173614351</v>
       </c>
       <c r="H3" t="n">
-        <v>241.7346173614335</v>
+        <v>241.7346173614351</v>
       </c>
       <c r="I3" t="n">
-        <v>30.1199146314645</v>
+        <v>30.11991463146613</v>
       </c>
       <c r="J3" t="n">
-        <v>174.7984703728012</v>
+        <v>174.7984703728029</v>
       </c>
       <c r="K3" t="n">
-        <v>399.4085458068072</v>
+        <v>399.4085458068089</v>
       </c>
       <c r="L3" t="n">
-        <v>718.3818833454036</v>
+        <v>718.3818833454052</v>
       </c>
       <c r="M3" t="n">
-        <v>860.0360750882628</v>
+        <v>860.0360750882644</v>
       </c>
       <c r="N3" t="n">
-        <v>1050.360878846775</v>
+        <v>1050.360878846776</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.587921002191</v>
+        <v>1341.587921002193</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.738421006376</v>
+        <v>1349.738421006378</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.871311105555</v>
+        <v>1214.871311105557</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.791656100326</v>
+        <v>1151.791656100327</v>
       </c>
       <c r="T3" t="n">
-        <v>1147.281782714996</v>
+        <v>774.0138783225489</v>
       </c>
       <c r="U3" t="n">
-        <v>1147.084020807432</v>
+        <v>773.8161164149845</v>
       </c>
       <c r="V3" t="n">
-        <v>769.3062430296541</v>
+        <v>759.1588768275905</v>
       </c>
       <c r="W3" t="n">
-        <v>736.6060986762919</v>
+        <v>726.4587324742283</v>
       </c>
       <c r="X3" t="n">
-        <v>358.8283208985141</v>
+        <v>706.3953592970691</v>
       </c>
       <c r="Y3" t="n">
-        <v>358.8283208985141</v>
+        <v>706.3953592970691</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>427.5120134985457</v>
+        <v>214.7295720284371</v>
       </c>
       <c r="C4" t="n">
-        <v>427.5120134985457</v>
+        <v>214.7295720284371</v>
       </c>
       <c r="D4" t="n">
-        <v>427.5120134985457</v>
+        <v>328.0487161534372</v>
       </c>
       <c r="E4" t="n">
-        <v>545.3409177099587</v>
+        <v>328.0487161534372</v>
       </c>
       <c r="F4" t="n">
-        <v>545.3409177099587</v>
+        <v>328.0487161534372</v>
       </c>
       <c r="G4" t="n">
-        <v>698.9313639247129</v>
+        <v>481.6391623681914</v>
       </c>
       <c r="H4" t="n">
-        <v>698.9313639247129</v>
+        <v>652.7906108062774</v>
       </c>
       <c r="I4" t="n">
-        <v>925.5940258116154</v>
+        <v>879.45327269318</v>
       </c>
       <c r="J4" t="n">
-        <v>1253.739110653045</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K4" t="n">
-        <v>1385.467095409585</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L4" t="n">
         <v>1385.467095409585</v>
@@ -4503,28 +4503,28 @@
         <v>351.3853387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>42.83865376875971</v>
       </c>
       <c r="T4" t="n">
-        <v>29.92</v>
+        <v>42.83865376875971</v>
       </c>
       <c r="U4" t="n">
-        <v>276.4812224743522</v>
+        <v>42.83865376875971</v>
       </c>
       <c r="V4" t="n">
-        <v>276.4812224743522</v>
+        <v>42.83865376875971</v>
       </c>
       <c r="W4" t="n">
-        <v>276.4812224743522</v>
+        <v>214.7295720284371</v>
       </c>
       <c r="X4" t="n">
-        <v>427.5120134985457</v>
+        <v>214.7295720284371</v>
       </c>
       <c r="Y4" t="n">
-        <v>427.5120134985457</v>
+        <v>214.7295720284371</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.8416377852028</v>
+        <v>108.8416377852044</v>
       </c>
       <c r="C5" t="n">
-        <v>58.86731632763319</v>
+        <v>58.86731632763478</v>
       </c>
       <c r="D5" t="n">
-        <v>48.42372467121926</v>
+        <v>48.42372467122085</v>
       </c>
       <c r="E5" t="n">
-        <v>44.016361431958</v>
+        <v>44.0163614319596</v>
       </c>
       <c r="F5" t="n">
-        <v>39.07734253497633</v>
+        <v>39.07734253497792</v>
       </c>
       <c r="G5" t="n">
-        <v>35.70026987310013</v>
+        <v>35.70026987310172</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.89313783918486</v>
       </c>
       <c r="I5" t="n">
-        <v>29.92</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="J5" t="n">
-        <v>30.01969029977264</v>
+        <v>30.01969029977267</v>
       </c>
       <c r="K5" t="n">
-        <v>400.2796902997726</v>
+        <v>82.16427879223498</v>
       </c>
       <c r="L5" t="n">
-        <v>464.9696632645968</v>
+        <v>326.5557936111291</v>
       </c>
       <c r="M5" t="n">
-        <v>835.2296632645968</v>
+        <v>696.8157936111295</v>
       </c>
       <c r="N5" t="n">
-        <v>1205.489663264597</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="O5" t="n">
-        <v>1205.489663264597</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="P5" t="n">
-        <v>1264.153869653468</v>
+        <v>1125.740000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="R5" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.724707412506</v>
+        <v>1409.724707412507</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.994415731961</v>
+        <v>1222.994415731962</v>
       </c>
       <c r="U5" t="n">
-        <v>971.2891925799706</v>
+        <v>971.2891925799722</v>
       </c>
       <c r="V5" t="n">
-        <v>739.1164408963101</v>
+        <v>739.1164408963117</v>
       </c>
       <c r="W5" t="n">
-        <v>498.3351520266661</v>
+        <v>498.3351520266677</v>
       </c>
       <c r="X5" t="n">
-        <v>304.1110778239714</v>
+        <v>304.111077823973</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.6692266292175</v>
+        <v>191.6692266292191</v>
       </c>
     </row>
     <row r="6">
@@ -4613,31 +4613,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1225.724928051676</v>
+        <v>701.8833331878382</v>
       </c>
       <c r="C6" t="n">
-        <v>1070.572551977265</v>
+        <v>701.8833331878382</v>
       </c>
       <c r="D6" t="n">
-        <v>719.1203429896864</v>
+        <v>350.4311242002597</v>
       </c>
       <c r="E6" t="n">
-        <v>372.9869114524009</v>
+        <v>350.4311242002597</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>350.4311242002597</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>350.4311242002597</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="I6" t="n">
-        <v>29.92</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="J6" t="n">
-        <v>174.5985557413367</v>
+        <v>174.5985557413368</v>
       </c>
       <c r="K6" t="n">
         <v>399.2086311753428</v>
@@ -4658,31 +4658,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1495.800085368536</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R6" t="n">
-        <v>1360.932975467714</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S6" t="n">
-        <v>1297.853320462485</v>
+        <v>1151.591741468861</v>
       </c>
       <c r="T6" t="n">
-        <v>1293.343447077155</v>
+        <v>1147.081868083532</v>
       </c>
       <c r="U6" t="n">
-        <v>1293.145685169591</v>
+        <v>769.3040903057536</v>
       </c>
       <c r="V6" t="n">
-        <v>1278.488445582197</v>
+        <v>754.6468507183595</v>
       </c>
       <c r="W6" t="n">
-        <v>1245.788301228835</v>
+        <v>721.9467063649973</v>
       </c>
       <c r="X6" t="n">
-        <v>1225.724928051676</v>
+        <v>701.8833331878382</v>
       </c>
       <c r="Y6" t="n">
-        <v>1225.724928051676</v>
+        <v>701.8833331878382</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>855.9250003280562</v>
+        <v>1250.707100357226</v>
       </c>
       <c r="C7" t="n">
-        <v>855.9250003280562</v>
+        <v>1376.709106175661</v>
       </c>
       <c r="D7" t="n">
-        <v>855.9250003280562</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="E7" t="n">
-        <v>855.9250003280562</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="F7" t="n">
-        <v>855.9250003280562</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="G7" t="n">
-        <v>855.9250003280562</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="H7" t="n">
-        <v>1027.076448766142</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="I7" t="n">
-        <v>1253.739110653045</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="J7" t="n">
-        <v>1253.739110653045</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K7" t="n">
         <v>1385.467095409585</v>
@@ -4740,28 +4740,28 @@
         <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
-        <v>29.92</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.37478771712395</v>
       </c>
       <c r="T7" t="n">
-        <v>218.7813496506081</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U7" t="n">
-        <v>465.3425721249604</v>
+        <v>505.7973598420843</v>
       </c>
       <c r="V7" t="n">
-        <v>664.1639650109064</v>
+        <v>704.6187527280304</v>
       </c>
       <c r="W7" t="n">
-        <v>836.0548832705838</v>
+        <v>876.5096709877078</v>
       </c>
       <c r="X7" t="n">
-        <v>855.9250003280562</v>
+        <v>1027.540462011901</v>
       </c>
       <c r="Y7" t="n">
-        <v>855.9250003280562</v>
+        <v>1138.949762690934</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.8416377852028</v>
+        <v>106.8684999460196</v>
       </c>
       <c r="C8" t="n">
-        <v>58.86731632763319</v>
+        <v>56.89417848844995</v>
       </c>
       <c r="D8" t="n">
-        <v>48.42372467121926</v>
+        <v>46.45058683203602</v>
       </c>
       <c r="E8" t="n">
-        <v>44.016361431958</v>
+        <v>42.04322359277477</v>
       </c>
       <c r="F8" t="n">
-        <v>39.07734253497633</v>
+        <v>37.10420469579309</v>
       </c>
       <c r="G8" t="n">
-        <v>35.70026987310013</v>
+        <v>33.72713203391689</v>
       </c>
       <c r="H8" t="n">
-        <v>31.89313783918327</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="I8" t="n">
-        <v>29.92</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="J8" t="n">
-        <v>30.01969029977264</v>
+        <v>30.01969029977267</v>
       </c>
       <c r="K8" t="n">
-        <v>82.16427879223495</v>
+        <v>400.2796902997731</v>
       </c>
       <c r="L8" t="n">
-        <v>326.5557936111288</v>
+        <v>464.9696632645972</v>
       </c>
       <c r="M8" t="n">
-        <v>696.8157936111288</v>
+        <v>835.2296632645975</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.075793611129</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.075793611129</v>
+        <v>1067.07579361113</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1125.740000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="R8" t="n">
-        <v>1496</v>
+        <v>1496.000000000002</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.724707412506</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.994415731961</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U8" t="n">
-        <v>971.2891925799706</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V8" t="n">
-        <v>739.1164408963101</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W8" t="n">
-        <v>498.3351520266661</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X8" t="n">
-        <v>304.1110778239714</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.6692266292175</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="9">
@@ -4850,31 +4850,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>574.8967309533409</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="C9" t="n">
-        <v>574.8967309533409</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="D9" t="n">
-        <v>574.8967309533409</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="E9" t="n">
-        <v>574.8967309533409</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="F9" t="n">
-        <v>574.8967309533409</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="G9" t="n">
-        <v>574.8967309533409</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="H9" t="n">
-        <v>241.534702729969</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="I9" t="n">
-        <v>29.92</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="J9" t="n">
-        <v>174.5985557413367</v>
+        <v>174.5985557413368</v>
       </c>
       <c r="K9" t="n">
         <v>399.2086311753428</v>
@@ -4916,10 +4916,10 @@
         <v>1099.526722235211</v>
       </c>
       <c r="X9" t="n">
-        <v>1079.463349058052</v>
+        <v>721.748944457433</v>
       </c>
       <c r="Y9" t="n">
-        <v>701.6855712802744</v>
+        <v>343.9711666796548</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>774.8297405151413</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="C10" t="n">
-        <v>900.8317463335771</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="D10" t="n">
-        <v>1014.150890458577</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="E10" t="n">
-        <v>1131.97979466999</v>
+        <v>573.9477435615022</v>
       </c>
       <c r="F10" t="n">
-        <v>1256.340767261926</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="G10" t="n">
-        <v>1385.467095409585</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="H10" t="n">
-        <v>1385.467095409585</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I10" t="n">
-        <v>1385.467095409585</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J10" t="n">
-        <v>1385.467095409585</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K10" t="n">
-        <v>1385.467095409585</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L10" t="n">
         <v>1385.467095409585</v>
@@ -4977,28 +4977,28 @@
         <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
-        <v>29.92</v>
+        <v>29.92000000000003</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712395</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="V10" t="n">
-        <v>228.741392885946</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="W10" t="n">
-        <v>400.6323111456234</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="X10" t="n">
-        <v>551.6631021698169</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="Y10" t="n">
-        <v>663.0724028488492</v>
+        <v>456.1188393500892</v>
       </c>
     </row>
     <row r="11">
@@ -5011,64 +5011,64 @@
         <v>596.4384060421568</v>
       </c>
       <c r="C11" t="n">
-        <v>466.6661047866073</v>
+        <v>466.6661047866074</v>
       </c>
       <c r="D11" t="n">
         <v>376.4245333322136</v>
       </c>
       <c r="E11" t="n">
-        <v>292.2191902949725</v>
+        <v>292.2191902949726</v>
       </c>
       <c r="F11" t="n">
-        <v>207.482191600011</v>
+        <v>207.4821916000111</v>
       </c>
       <c r="G11" t="n">
         <v>125.2979517892592</v>
       </c>
       <c r="H11" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I11" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J11" t="n">
-        <v>134.360205073642</v>
+        <v>560.3618942939372</v>
       </c>
       <c r="K11" t="n">
-        <v>310.0317798977626</v>
+        <v>736.0334691180578</v>
       </c>
       <c r="L11" t="n">
-        <v>951.5517798977626</v>
+        <v>1199.603921654829</v>
       </c>
       <c r="M11" t="n">
-        <v>1593.071779897763</v>
+        <v>1199.603921654829</v>
       </c>
       <c r="N11" t="n">
-        <v>2230.549243836214</v>
+        <v>1199.603921654829</v>
       </c>
       <c r="O11" t="n">
-        <v>2393.691050093541</v>
+        <v>1362.745727912156</v>
       </c>
       <c r="P11" t="n">
-        <v>2592</v>
+        <v>2004.265727912159</v>
       </c>
       <c r="Q11" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="R11" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="S11" t="n">
-        <v>2448.504870855986</v>
+        <v>2451.490786871937</v>
       </c>
       <c r="T11" t="n">
-        <v>2186.313881748914</v>
+        <v>2189.299797764865</v>
       </c>
       <c r="U11" t="n">
-        <v>1854.889943810872</v>
+        <v>1857.875859826824</v>
       </c>
       <c r="V11" t="n">
-        <v>1542.919212329232</v>
+        <v>1545.905128345183</v>
       </c>
       <c r="W11" t="n">
         <v>1225.325859677559</v>
@@ -5087,28 +5087,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>685.9081767935552</v>
+        <v>816.7882329734397</v>
       </c>
       <c r="C12" t="n">
-        <v>645.4032147273741</v>
+        <v>452.0408466648343</v>
       </c>
       <c r="D12" t="n">
-        <v>618.19342998222</v>
+        <v>424.8310619196801</v>
       </c>
       <c r="E12" t="n">
-        <v>596.3024226873588</v>
+        <v>402.9400546248189</v>
       </c>
       <c r="F12" t="n">
-        <v>577.4779354773822</v>
+        <v>384.1155674148422</v>
       </c>
       <c r="G12" t="n">
-        <v>249.2020177839106</v>
+        <v>380.082073963795</v>
       </c>
       <c r="H12" t="n">
-        <v>245.20236806254</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I12" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J12" t="n">
         <v>245.6076497036009</v>
@@ -5138,25 +5138,25 @@
         <v>2071.399071663636</v>
       </c>
       <c r="S12" t="n">
-        <v>1938.368397028141</v>
+        <v>1753.359036645168</v>
       </c>
       <c r="T12" t="n">
-        <v>1856.197345826917</v>
+        <v>1671.187985443944</v>
       </c>
       <c r="U12" t="n">
-        <v>1776.236481193986</v>
+        <v>1591.227120811013</v>
       </c>
       <c r="V12" t="n">
-        <v>1681.781261808612</v>
+        <v>1496.771901425639</v>
       </c>
       <c r="W12" t="n">
-        <v>1253.393721094412</v>
+        <v>1384.273777274297</v>
       </c>
       <c r="X12" t="n">
-        <v>829.2899438768491</v>
+        <v>960.1700000567336</v>
       </c>
       <c r="Y12" t="n">
-        <v>750.1067188605517</v>
+        <v>880.9867750404362</v>
       </c>
     </row>
     <row r="13">
@@ -5166,25 +5166,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>681.4588756890412</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C13" t="n">
-        <v>729.2508815074769</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D13" t="n">
-        <v>764.360025632477</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E13" t="n">
-        <v>803.97892984389</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F13" t="n">
-        <v>850.1299024358254</v>
+        <v>855.2582993868861</v>
       </c>
       <c r="G13" t="n">
-        <v>925.9459486505796</v>
+        <v>931.0743456016402</v>
       </c>
       <c r="H13" t="n">
-        <v>1022.760277088666</v>
+        <v>1027.888674039726</v>
       </c>
       <c r="I13" t="n">
         <v>1184.312618975568</v>
@@ -5208,34 +5208,34 @@
         <v>1113.602925280855</v>
       </c>
       <c r="P13" t="n">
-        <v>819.8981109568782</v>
+        <v>819.8981109568783</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.8958216380924</v>
+        <v>463.8958216380925</v>
       </c>
       <c r="R13" t="n">
-        <v>82.61634147829413</v>
+        <v>82.61634147829417</v>
       </c>
       <c r="S13" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="T13" t="n">
-        <v>159.2241526995476</v>
+        <v>164.3525496506082</v>
       </c>
       <c r="U13" t="n">
-        <v>327.5991351738998</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V13" t="n">
-        <v>448.2105280598458</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W13" t="n">
-        <v>541.8914463195232</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X13" t="n">
-        <v>614.7122373437168</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y13" t="n">
-        <v>647.911538022749</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="14">
@@ -5245,28 +5245,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.4384060421568</v>
+        <v>593.4524900262279</v>
       </c>
       <c r="C14" t="n">
-        <v>466.6661047866073</v>
+        <v>463.6801887706785</v>
       </c>
       <c r="D14" t="n">
-        <v>376.4245333322136</v>
+        <v>373.4386173162847</v>
       </c>
       <c r="E14" t="n">
-        <v>292.2191902949725</v>
+        <v>289.2332742790437</v>
       </c>
       <c r="F14" t="n">
-        <v>207.482191600011</v>
+        <v>204.4962755840822</v>
       </c>
       <c r="G14" t="n">
-        <v>125.2979517892592</v>
+        <v>122.3120357733303</v>
       </c>
       <c r="H14" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I14" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J14" t="n">
         <v>134.360205073642</v>
@@ -5275,46 +5275,46 @@
         <v>310.0317798977626</v>
       </c>
       <c r="L14" t="n">
-        <v>951.5517798977626</v>
+        <v>947.5092438362086</v>
       </c>
       <c r="M14" t="n">
-        <v>1589.029243836214</v>
+        <v>1589.029243836212</v>
       </c>
       <c r="N14" t="n">
-        <v>2230.549243836214</v>
+        <v>2230.549243836216</v>
       </c>
       <c r="O14" t="n">
-        <v>2393.691050093541</v>
+        <v>2393.691050093543</v>
       </c>
       <c r="P14" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="R14" t="n">
-        <v>2592</v>
+        <v>2592.000000000022</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.490786871937</v>
+        <v>2448.504870856008</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.299797764865</v>
+        <v>2186.313881748936</v>
       </c>
       <c r="U14" t="n">
-        <v>1857.875859826824</v>
+        <v>1854.889943810895</v>
       </c>
       <c r="V14" t="n">
-        <v>1545.905128345183</v>
+        <v>1542.919212329254</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.325859677559</v>
+        <v>1222.339943661631</v>
       </c>
       <c r="X14" t="n">
-        <v>951.3038056768851</v>
+        <v>948.3178896609561</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.0639746841513</v>
+        <v>756.0780586682224</v>
       </c>
     </row>
     <row r="15">
@@ -5324,28 +5324,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>168.3033844885911</v>
+        <v>1247.449260026979</v>
       </c>
       <c r="C15" t="n">
-        <v>127.79842242241</v>
+        <v>1206.944297960798</v>
       </c>
       <c r="D15" t="n">
-        <v>100.5886376772558</v>
+        <v>855.4920889732193</v>
       </c>
       <c r="E15" t="n">
-        <v>78.69763038239455</v>
+        <v>833.6010816783581</v>
       </c>
       <c r="F15" t="n">
-        <v>59.87314317241791</v>
+        <v>490.5341702259572</v>
       </c>
       <c r="G15" t="n">
-        <v>55.83964972137068</v>
+        <v>162.2582525324857</v>
       </c>
       <c r="H15" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I15" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J15" t="n">
         <v>245.6076497036009</v>
@@ -5369,31 +5369,31 @@
         <v>2253.149505368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2253.149505368536</v>
+        <v>2174.558747796677</v>
       </c>
       <c r="R15" t="n">
-        <v>2071.399071663636</v>
+        <v>1992.808314091777</v>
       </c>
       <c r="S15" t="n">
-        <v>1938.368397028141</v>
+        <v>1859.777639456283</v>
       </c>
       <c r="T15" t="n">
-        <v>1856.197345826917</v>
+        <v>1777.606588255059</v>
       </c>
       <c r="U15" t="n">
-        <v>1776.236481193986</v>
+        <v>1697.645723622128</v>
       </c>
       <c r="V15" t="n">
-        <v>1357.538837566188</v>
+        <v>1603.190504236754</v>
       </c>
       <c r="W15" t="n">
-        <v>920.7982891724216</v>
+        <v>1490.692380085412</v>
       </c>
       <c r="X15" t="n">
-        <v>496.6945119548584</v>
+        <v>1390.831027110273</v>
       </c>
       <c r="Y15" t="n">
-        <v>232.5019265555877</v>
+        <v>1311.647802093976</v>
       </c>
     </row>
     <row r="16">
@@ -5406,13 +5406,13 @@
         <v>686.5872726401018</v>
       </c>
       <c r="C16" t="n">
-        <v>729.2508815074769</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D16" t="n">
-        <v>764.360025632477</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E16" t="n">
-        <v>803.97892984389</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F16" t="n">
         <v>850.1299024358254</v>
@@ -5445,19 +5445,19 @@
         <v>1113.602925280855</v>
       </c>
       <c r="P16" t="n">
-        <v>819.8981109568782</v>
+        <v>819.8981109568783</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.8958216380924</v>
+        <v>463.8958216380925</v>
       </c>
       <c r="R16" t="n">
-        <v>82.61634147829413</v>
+        <v>82.61634147829417</v>
       </c>
       <c r="S16" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="T16" t="n">
-        <v>164.3525496506081</v>
+        <v>164.3525496506082</v>
       </c>
       <c r="U16" t="n">
         <v>332.7275321249604</v>
@@ -5485,73 +5485,73 @@
         <v>596.4384060421568</v>
       </c>
       <c r="C17" t="n">
-        <v>466.6661047866073</v>
+        <v>466.6661047866074</v>
       </c>
       <c r="D17" t="n">
         <v>376.4245333322136</v>
       </c>
       <c r="E17" t="n">
-        <v>292.2191902949725</v>
+        <v>292.2191902949726</v>
       </c>
       <c r="F17" t="n">
-        <v>207.482191600011</v>
+        <v>207.4821916000111</v>
       </c>
       <c r="G17" t="n">
         <v>125.2979517892592</v>
       </c>
       <c r="H17" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I17" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J17" t="n">
         <v>134.360205073642</v>
       </c>
       <c r="K17" t="n">
-        <v>729.5731213236512</v>
+        <v>310.0317798977626</v>
       </c>
       <c r="L17" t="n">
-        <v>947.509243836214</v>
+        <v>527.9679024103255</v>
       </c>
       <c r="M17" t="n">
-        <v>1589.029243836214</v>
+        <v>1169.48790241033</v>
       </c>
       <c r="N17" t="n">
-        <v>2230.549243836214</v>
+        <v>1811.007902410334</v>
       </c>
       <c r="O17" t="n">
-        <v>2393.691050093541</v>
+        <v>1974.149708667661</v>
       </c>
       <c r="P17" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="Q17" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="R17" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="S17" t="n">
-        <v>2448.504870855986</v>
+        <v>2448.504870855988</v>
       </c>
       <c r="T17" t="n">
-        <v>2186.313881748914</v>
+        <v>2186.313881748916</v>
       </c>
       <c r="U17" t="n">
-        <v>1854.889943810872</v>
+        <v>1854.889943810874</v>
       </c>
       <c r="V17" t="n">
-        <v>1542.919212329232</v>
+        <v>1542.919212329234</v>
       </c>
       <c r="W17" t="n">
-        <v>1222.339943661608</v>
+        <v>1222.33994366161</v>
       </c>
       <c r="X17" t="n">
-        <v>948.3178896609338</v>
+        <v>948.3178896609356</v>
       </c>
       <c r="Y17" t="n">
-        <v>756.0780586682001</v>
+        <v>756.0780586682019</v>
       </c>
     </row>
     <row r="18">
@@ -5561,28 +5561,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>168.3033844885911</v>
+        <v>1326.040017598837</v>
       </c>
       <c r="C18" t="n">
-        <v>127.79842242241</v>
+        <v>961.2926312902318</v>
       </c>
       <c r="D18" t="n">
-        <v>100.5886376772558</v>
+        <v>609.8404223026535</v>
       </c>
       <c r="E18" t="n">
-        <v>78.69763038239455</v>
+        <v>263.7069907653679</v>
       </c>
       <c r="F18" t="n">
-        <v>59.87314317241791</v>
+        <v>244.8825035553913</v>
       </c>
       <c r="G18" t="n">
-        <v>55.83964972137068</v>
+        <v>240.8490101043441</v>
       </c>
       <c r="H18" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I18" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J18" t="n">
         <v>245.6076497036009</v>
@@ -5618,19 +5618,19 @@
         <v>1856.197345826917</v>
       </c>
       <c r="U18" t="n">
-        <v>1451.994056951562</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V18" t="n">
-        <v>1033.296413323764</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W18" t="n">
-        <v>596.5558649299974</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X18" t="n">
-        <v>311.685151571885</v>
+        <v>1469.421784682131</v>
       </c>
       <c r="Y18" t="n">
-        <v>232.5019265555877</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="19">
@@ -5646,13 +5646,13 @@
         <v>734.3792784585376</v>
       </c>
       <c r="D19" t="n">
-        <v>764.360025632477</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E19" t="n">
-        <v>803.97892984389</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F19" t="n">
-        <v>850.1299024358254</v>
+        <v>855.2582993868861</v>
       </c>
       <c r="G19" t="n">
         <v>925.9459486505796</v>
@@ -5682,19 +5682,19 @@
         <v>1113.602925280855</v>
       </c>
       <c r="P19" t="n">
-        <v>819.8981109568782</v>
+        <v>819.8981109568783</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.8958216380924</v>
+        <v>463.8958216380925</v>
       </c>
       <c r="R19" t="n">
-        <v>82.61634147829413</v>
+        <v>82.61634147829417</v>
       </c>
       <c r="S19" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="T19" t="n">
-        <v>164.3525496506081</v>
+        <v>164.3525496506082</v>
       </c>
       <c r="U19" t="n">
         <v>332.7275321249604</v>
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>593.4524900262272</v>
+        <v>593.4524900262409</v>
       </c>
       <c r="C20" t="n">
-        <v>463.6801887706778</v>
+        <v>463.6801887706914</v>
       </c>
       <c r="D20" t="n">
-        <v>373.438617316284</v>
+        <v>373.4386173162977</v>
       </c>
       <c r="E20" t="n">
-        <v>289.233274279043</v>
+        <v>289.2332742790566</v>
       </c>
       <c r="F20" t="n">
-        <v>204.4962755840815</v>
+        <v>204.4962755840951</v>
       </c>
       <c r="G20" t="n">
-        <v>122.3120357733296</v>
+        <v>122.3120357733433</v>
       </c>
       <c r="H20" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I20" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J20" t="n">
-        <v>560.3618942939371</v>
+        <v>560.3618942939372</v>
       </c>
       <c r="K20" t="n">
-        <v>736.0334691180577</v>
+        <v>736.0334691180578</v>
       </c>
       <c r="L20" t="n">
         <v>953.9695916306206</v>
       </c>
       <c r="M20" t="n">
-        <v>1595.48959163062</v>
+        <v>1164.436778005695</v>
       </c>
       <c r="N20" t="n">
-        <v>1642.814971748371</v>
+        <v>1164.436778005695</v>
       </c>
       <c r="O20" t="n">
-        <v>1805.956778005698</v>
+        <v>1805.9567780057</v>
       </c>
       <c r="P20" t="n">
-        <v>2004.265727912157</v>
+        <v>2004.265727912159</v>
       </c>
       <c r="Q20" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="R20" t="n">
-        <v>2592.000000000021</v>
+        <v>2592.000000000035</v>
       </c>
       <c r="S20" t="n">
-        <v>2448.504870856007</v>
+        <v>2448.504870856021</v>
       </c>
       <c r="T20" t="n">
-        <v>2186.313881748935</v>
+        <v>2186.313881748949</v>
       </c>
       <c r="U20" t="n">
-        <v>1854.889943810894</v>
+        <v>1854.889943810908</v>
       </c>
       <c r="V20" t="n">
-        <v>1542.919212329254</v>
+        <v>1542.919212329267</v>
       </c>
       <c r="W20" t="n">
-        <v>1222.33994366163</v>
+        <v>1222.339943661643</v>
       </c>
       <c r="X20" t="n">
-        <v>948.3178896609554</v>
+        <v>948.3178896609691</v>
       </c>
       <c r="Y20" t="n">
-        <v>756.0780586682217</v>
+        <v>756.0780586682354</v>
       </c>
     </row>
     <row r="21">
@@ -5807,19 +5807,19 @@
         <v>100.5886376772558</v>
       </c>
       <c r="E21" t="n">
-        <v>78.69763038239458</v>
+        <v>78.69763038239461</v>
       </c>
       <c r="F21" t="n">
-        <v>59.87314317241794</v>
+        <v>59.87314317241798</v>
       </c>
       <c r="G21" t="n">
-        <v>55.83964972137069</v>
+        <v>55.83964972137073</v>
       </c>
       <c r="H21" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I21" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J21" t="n">
         <v>245.6076497036009</v>
@@ -5846,22 +5846,22 @@
         <v>2174.558747796677</v>
       </c>
       <c r="R21" t="n">
-        <v>1668.565889849353</v>
+        <v>1992.808314091777</v>
       </c>
       <c r="S21" t="n">
-        <v>1535.535215213859</v>
+        <v>1859.777639456283</v>
       </c>
       <c r="T21" t="n">
-        <v>1129.12173977021</v>
+        <v>1777.606588255059</v>
       </c>
       <c r="U21" t="n">
-        <v>724.9184508948549</v>
+        <v>1373.403299379703</v>
       </c>
       <c r="V21" t="n">
-        <v>630.463231509481</v>
+        <v>954.7056557519052</v>
       </c>
       <c r="W21" t="n">
-        <v>411.546504547024</v>
+        <v>517.965107358139</v>
       </c>
       <c r="X21" t="n">
         <v>311.6851515718851</v>
@@ -5889,16 +5889,16 @@
         <v>809.1073267949506</v>
       </c>
       <c r="F22" t="n">
-        <v>850.1299024358254</v>
+        <v>855.2582993868861</v>
       </c>
       <c r="G22" t="n">
-        <v>925.9459486505796</v>
+        <v>931.0743456016402</v>
       </c>
       <c r="H22" t="n">
-        <v>1022.760277088666</v>
+        <v>1027.888674039726</v>
       </c>
       <c r="I22" t="n">
-        <v>1184.312618975568</v>
+        <v>1189.441015926629</v>
       </c>
       <c r="J22" t="n">
         <v>1510.983618808348</v>
@@ -5919,19 +5919,19 @@
         <v>1113.602925280855</v>
       </c>
       <c r="P22" t="n">
-        <v>819.8981109568782</v>
+        <v>819.8981109568783</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.8958216380923</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R22" t="n">
-        <v>82.61634147829412</v>
+        <v>82.61634147829416</v>
       </c>
       <c r="S22" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="T22" t="n">
-        <v>164.3525496506081</v>
+        <v>164.3525496506082</v>
       </c>
       <c r="U22" t="n">
         <v>332.7275321249604</v>
@@ -5956,28 +5956,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>596.4384060421568</v>
+        <v>593.4524900262074</v>
       </c>
       <c r="C23" t="n">
-        <v>466.6661047866073</v>
+        <v>463.680188770658</v>
       </c>
       <c r="D23" t="n">
-        <v>376.4245333322136</v>
+        <v>373.4386173162642</v>
       </c>
       <c r="E23" t="n">
-        <v>292.2191902949725</v>
+        <v>289.2332742790232</v>
       </c>
       <c r="F23" t="n">
-        <v>207.482191600011</v>
+        <v>204.4962755840617</v>
       </c>
       <c r="G23" t="n">
         <v>125.2979517892592</v>
       </c>
       <c r="H23" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I23" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J23" t="n">
         <v>134.360205073642</v>
@@ -5986,46 +5986,46 @@
         <v>310.0317798977626</v>
       </c>
       <c r="L23" t="n">
-        <v>951.5517798977626</v>
+        <v>527.9679024103255</v>
       </c>
       <c r="M23" t="n">
-        <v>1593.071779897763</v>
+        <v>1145.818193742674</v>
       </c>
       <c r="N23" t="n">
-        <v>2230.549243836214</v>
+        <v>1787.338193742675</v>
       </c>
       <c r="O23" t="n">
-        <v>2393.691050093541</v>
+        <v>1950.480000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="Q23" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="R23" t="n">
-        <v>2592</v>
+        <v>2592.000000000002</v>
       </c>
       <c r="S23" t="n">
-        <v>2451.490786871937</v>
+        <v>2448.504870855988</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.299797764865</v>
+        <v>2186.313881748916</v>
       </c>
       <c r="U23" t="n">
-        <v>1857.875859826824</v>
+        <v>1854.889943810874</v>
       </c>
       <c r="V23" t="n">
-        <v>1545.905128345183</v>
+        <v>1542.919212329234</v>
       </c>
       <c r="W23" t="n">
-        <v>1225.325859677559</v>
+        <v>1222.33994366161</v>
       </c>
       <c r="X23" t="n">
-        <v>951.3038056768851</v>
+        <v>948.3178896609356</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.0639746841513</v>
+        <v>756.0780586682019</v>
       </c>
     </row>
     <row r="24">
@@ -6044,19 +6044,19 @@
         <v>100.5886376772558</v>
       </c>
       <c r="E24" t="n">
-        <v>78.69763038239455</v>
+        <v>78.69763038239458</v>
       </c>
       <c r="F24" t="n">
-        <v>59.87314317241791</v>
+        <v>59.87314317241795</v>
       </c>
       <c r="G24" t="n">
-        <v>55.83964972137068</v>
+        <v>55.83964972137071</v>
       </c>
       <c r="H24" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="I24" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="J24" t="n">
         <v>245.6076497036009</v>
@@ -6080,28 +6080,28 @@
         <v>2253.149505368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2174.558747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1992.808314091777</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S24" t="n">
-        <v>1859.777639456283</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T24" t="n">
-        <v>1777.606588255059</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U24" t="n">
-        <v>1373.403299379703</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V24" t="n">
-        <v>1278.948079994329</v>
+        <v>1496.771901425639</v>
       </c>
       <c r="W24" t="n">
-        <v>842.2075316005632</v>
+        <v>1060.031353031873</v>
       </c>
       <c r="X24" t="n">
-        <v>635.9275758143092</v>
+        <v>635.9275758143093</v>
       </c>
       <c r="Y24" t="n">
         <v>232.5019265555877</v>
@@ -6114,13 +6114,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>681.4588756890412</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C25" t="n">
-        <v>729.2508815074769</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D25" t="n">
-        <v>764.360025632477</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E25" t="n">
         <v>803.97892984389</v>
@@ -6156,34 +6156,34 @@
         <v>1113.602925280855</v>
       </c>
       <c r="P25" t="n">
-        <v>819.8981109568782</v>
+        <v>819.8981109568783</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.8958216380924</v>
+        <v>463.8958216380925</v>
       </c>
       <c r="R25" t="n">
-        <v>82.61634147829413</v>
+        <v>82.61634147829417</v>
       </c>
       <c r="S25" t="n">
-        <v>51.84</v>
+        <v>51.84000000000004</v>
       </c>
       <c r="T25" t="n">
-        <v>159.2241526995476</v>
+        <v>164.3525496506082</v>
       </c>
       <c r="U25" t="n">
-        <v>327.5991351738998</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V25" t="n">
-        <v>448.2105280598458</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W25" t="n">
-        <v>541.8914463195232</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X25" t="n">
-        <v>614.7122373437168</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y25" t="n">
-        <v>647.911538022749</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>596.5184060421568</v>
+        <v>597.4524900262056</v>
       </c>
       <c r="C26" t="n">
-        <v>466.7461047866074</v>
+        <v>467.6801887706562</v>
       </c>
       <c r="D26" t="n">
-        <v>376.5045333322136</v>
+        <v>377.4386173162624</v>
       </c>
       <c r="E26" t="n">
-        <v>292.2991902949726</v>
+        <v>293.2332742790214</v>
       </c>
       <c r="F26" t="n">
-        <v>207.5621916000111</v>
+        <v>208.4962755840599</v>
       </c>
       <c r="G26" t="n">
-        <v>125.3779517892592</v>
+        <v>126.3120357733081</v>
       </c>
       <c r="H26" t="n">
         <v>51.92</v>
@@ -6220,49 +6220,49 @@
         <v>134.440205073642</v>
       </c>
       <c r="K26" t="n">
-        <v>776.950205073642</v>
+        <v>310.1117798977626</v>
       </c>
       <c r="L26" t="n">
-        <v>994.8863275862049</v>
+        <v>949.5292438362139</v>
       </c>
       <c r="M26" t="n">
-        <v>1637.396327586206</v>
+        <v>1592.039243836214</v>
       </c>
       <c r="N26" t="n">
-        <v>1646.814971748371</v>
+        <v>2234.549243836214</v>
       </c>
       <c r="O26" t="n">
-        <v>1809.956778005698</v>
+        <v>2397.691050093541</v>
       </c>
       <c r="P26" t="n">
-        <v>2008.265727912157</v>
+        <v>2596</v>
       </c>
       <c r="Q26" t="n">
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2595.065916015951</v>
+        <v>2596</v>
       </c>
       <c r="S26" t="n">
-        <v>2451.570786871937</v>
+        <v>2452.504870855986</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.379797764865</v>
+        <v>2190.313881748914</v>
       </c>
       <c r="U26" t="n">
-        <v>1857.955859826824</v>
+        <v>1858.889943810872</v>
       </c>
       <c r="V26" t="n">
-        <v>1545.985128345183</v>
+        <v>1546.919212329232</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.405859677559</v>
+        <v>1226.339943661608</v>
       </c>
       <c r="X26" t="n">
-        <v>951.383805676885</v>
+        <v>952.3178896609338</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.1439746841513</v>
+        <v>760.0780586682001</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>492.6258087310154</v>
+        <v>168.383384488591</v>
       </c>
       <c r="C27" t="n">
-        <v>452.1208466648343</v>
+        <v>127.87842242241</v>
       </c>
       <c r="D27" t="n">
-        <v>424.9110619196801</v>
+        <v>100.6686376772558</v>
       </c>
       <c r="E27" t="n">
-        <v>403.0200546248188</v>
+        <v>78.77763038239453</v>
       </c>
       <c r="F27" t="n">
-        <v>384.1955674148422</v>
+        <v>59.95314317241791</v>
       </c>
       <c r="G27" t="n">
-        <v>55.91964972137069</v>
+        <v>55.91964972137067</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6326,22 +6326,22 @@
         <v>1859.857639456283</v>
       </c>
       <c r="T27" t="n">
-        <v>1671.267985443944</v>
+        <v>1777.686588255059</v>
       </c>
       <c r="U27" t="n">
-        <v>1591.307120811013</v>
+        <v>1697.725723622128</v>
       </c>
       <c r="V27" t="n">
-        <v>1496.851901425639</v>
+        <v>1603.270504236754</v>
       </c>
       <c r="W27" t="n">
-        <v>1384.353777274297</v>
+        <v>1166.529955842987</v>
       </c>
       <c r="X27" t="n">
-        <v>960.2500000567336</v>
+        <v>742.4261786254242</v>
       </c>
       <c r="Y27" t="n">
-        <v>556.824350798012</v>
+        <v>339.0005293667026</v>
       </c>
     </row>
     <row r="28">
@@ -6351,28 +6351,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>686.6672726401017</v>
+        <v>681.5388756890411</v>
       </c>
       <c r="C28" t="n">
-        <v>734.4592784585375</v>
+        <v>729.3308815074769</v>
       </c>
       <c r="D28" t="n">
-        <v>769.5684225835375</v>
+        <v>764.4400256324769</v>
       </c>
       <c r="E28" t="n">
-        <v>809.1873267949505</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F28" t="n">
-        <v>855.338299386886</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G28" t="n">
-        <v>931.1543456016401</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H28" t="n">
-        <v>1027.968674039726</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I28" t="n">
-        <v>1189.521015926629</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J28" t="n">
         <v>1511.063618808347</v>
@@ -6399,7 +6399,7 @@
         <v>463.9758216380924</v>
       </c>
       <c r="R28" t="n">
-        <v>82.69634147829412</v>
+        <v>82.69634147829413</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6408,19 +6408,19 @@
         <v>164.4325496506081</v>
       </c>
       <c r="U28" t="n">
-        <v>332.8075321249603</v>
+        <v>327.6791351738997</v>
       </c>
       <c r="V28" t="n">
-        <v>453.4189250109063</v>
+        <v>448.2905280598457</v>
       </c>
       <c r="W28" t="n">
-        <v>547.0998432705837</v>
+        <v>541.9714463195231</v>
       </c>
       <c r="X28" t="n">
-        <v>619.9206342947773</v>
+        <v>614.7922373437167</v>
       </c>
       <c r="Y28" t="n">
-        <v>653.1199349738096</v>
+        <v>647.991538022749</v>
       </c>
     </row>
     <row r="29">
@@ -6457,22 +6457,22 @@
         <v>134.440205073642</v>
       </c>
       <c r="K29" t="n">
-        <v>731.5931213236454</v>
+        <v>310.1117798977626</v>
       </c>
       <c r="L29" t="n">
-        <v>949.5292438362081</v>
+        <v>528.0479024103255</v>
       </c>
       <c r="M29" t="n">
-        <v>1592.039243836211</v>
+        <v>1004.304971748371</v>
       </c>
       <c r="N29" t="n">
-        <v>2234.549243836214</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="O29" t="n">
-        <v>2397.691050093541</v>
+        <v>1809.956778005698</v>
       </c>
       <c r="P29" t="n">
-        <v>2596</v>
+        <v>2008.265727912157</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>677.6351691139887</v>
+        <v>1141.110657215864</v>
       </c>
       <c r="C30" t="n">
-        <v>637.1302070478076</v>
+        <v>776.3632709072585</v>
       </c>
       <c r="D30" t="n">
-        <v>285.6779980602292</v>
+        <v>424.9110619196801</v>
       </c>
       <c r="E30" t="n">
-        <v>263.7869907653679</v>
+        <v>403.0200546248188</v>
       </c>
       <c r="F30" t="n">
-        <v>244.9625035553913</v>
+        <v>59.95314317241794</v>
       </c>
       <c r="G30" t="n">
-        <v>240.929010104344</v>
+        <v>55.91964972137069</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6575,10 +6575,10 @@
         <v>1569.36313765727</v>
       </c>
       <c r="X30" t="n">
-        <v>1145.259360439707</v>
+        <v>1469.501784682131</v>
       </c>
       <c r="Y30" t="n">
-        <v>1066.07613542341</v>
+        <v>1390.318559665834</v>
       </c>
     </row>
     <row r="31">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>686.6672726401017</v>
+        <v>681.5388756890411</v>
       </c>
       <c r="C31" t="n">
-        <v>734.4592784585375</v>
+        <v>729.3308815074769</v>
       </c>
       <c r="D31" t="n">
         <v>764.4400256324769</v>
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.5184060421568</v>
+        <v>596.5184060421567</v>
       </c>
       <c r="C32" t="n">
-        <v>466.7461047866074</v>
+        <v>466.7461047866073</v>
       </c>
       <c r="D32" t="n">
         <v>376.5045333322136</v>
       </c>
       <c r="E32" t="n">
-        <v>292.2991902949726</v>
+        <v>292.2991902949725</v>
       </c>
       <c r="F32" t="n">
-        <v>207.5621916000111</v>
+        <v>207.562191600011</v>
       </c>
       <c r="G32" t="n">
         <v>125.3779517892592</v>
@@ -6691,19 +6691,19 @@
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>560.4418942939371</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K32" t="n">
-        <v>736.1134691180577</v>
+        <v>776.950205073642</v>
       </c>
       <c r="L32" t="n">
-        <v>1112.671050093531</v>
+        <v>1419.460205073642</v>
       </c>
       <c r="M32" t="n">
-        <v>1112.671050093531</v>
+        <v>2061.970205073642</v>
       </c>
       <c r="N32" t="n">
-        <v>1755.181050093536</v>
+        <v>2234.549243836214</v>
       </c>
       <c r="O32" t="n">
         <v>2397.691050093541</v>
@@ -6736,7 +6736,7 @@
         <v>951.383805676885</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.1439746841513</v>
+        <v>759.1439746841512</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>816.8682329734396</v>
+        <v>168.383384488591</v>
       </c>
       <c r="C33" t="n">
-        <v>452.1208466648342</v>
+        <v>127.87842242241</v>
       </c>
       <c r="D33" t="n">
-        <v>424.91106191968</v>
+        <v>100.6686376772558</v>
       </c>
       <c r="E33" t="n">
-        <v>78.77763038239456</v>
+        <v>78.77763038239453</v>
       </c>
       <c r="F33" t="n">
-        <v>59.95314317241794</v>
+        <v>59.95314317241791</v>
       </c>
       <c r="G33" t="n">
-        <v>55.91964972137069</v>
+        <v>55.91964972137067</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6806,16 +6806,16 @@
         <v>1776.316481193986</v>
       </c>
       <c r="V33" t="n">
-        <v>1681.861261808612</v>
+        <v>1496.851901425639</v>
       </c>
       <c r="W33" t="n">
-        <v>1384.353777274297</v>
+        <v>1060.111353031873</v>
       </c>
       <c r="X33" t="n">
-        <v>1284.492424299158</v>
+        <v>636.0075758143092</v>
       </c>
       <c r="Y33" t="n">
-        <v>881.0667750404361</v>
+        <v>232.5819265555876</v>
       </c>
     </row>
     <row r="34">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>681.5388756890411</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C34" t="n">
         <v>729.3308815074769</v>
@@ -6873,7 +6873,7 @@
         <v>463.9758216380924</v>
       </c>
       <c r="R34" t="n">
-        <v>82.69634147829412</v>
+        <v>82.69634147829413</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6882,19 +6882,19 @@
         <v>164.4325496506081</v>
       </c>
       <c r="U34" t="n">
-        <v>327.6791351738997</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V34" t="n">
-        <v>448.2905280598457</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W34" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X34" t="n">
-        <v>614.7922373437167</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y34" t="n">
-        <v>647.991538022749</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="35">
@@ -6904,19 +6904,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>444.0238605876112</v>
+        <v>439.3918839655994</v>
       </c>
       <c r="C35" t="n">
-        <v>338.4939835744861</v>
+        <v>333.8620069524742</v>
       </c>
       <c r="D35" t="n">
-        <v>272.4948363625166</v>
+        <v>267.8628597405047</v>
       </c>
       <c r="E35" t="n">
-        <v>212.5319175676998</v>
+        <v>207.8999409456879</v>
       </c>
       <c r="F35" t="n">
-        <v>152.0373431151626</v>
+        <v>147.4053664931506</v>
       </c>
       <c r="G35" t="n">
         <v>94.09552754683496</v>
@@ -6931,22 +6931,22 @@
         <v>127.400205073642</v>
       </c>
       <c r="K35" t="n">
-        <v>303.0717798977627</v>
+        <v>682.790205073642</v>
       </c>
       <c r="L35" t="n">
-        <v>858.4617798977627</v>
+        <v>900.7263275862049</v>
       </c>
       <c r="M35" t="n">
-        <v>934.9110500935411</v>
+        <v>1456.116327586205</v>
       </c>
       <c r="N35" t="n">
-        <v>934.9110500935411</v>
+        <v>1525.468193742673</v>
       </c>
       <c r="O35" t="n">
-        <v>1490.301050093541</v>
+        <v>1688.61</v>
       </c>
       <c r="P35" t="n">
-        <v>1688.61</v>
+        <v>2244</v>
       </c>
       <c r="Q35" t="n">
         <v>2244</v>
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>952.0905464111607</v>
+        <v>761.0795952961838</v>
       </c>
       <c r="C36" t="n">
-        <v>935.8280085874039</v>
+        <v>396.3322089875784</v>
       </c>
       <c r="D36" t="n">
-        <v>584.3757995998254</v>
+        <v>44.88</v>
       </c>
       <c r="E36" t="n">
-        <v>238.24236806254</v>
+        <v>44.88</v>
       </c>
       <c r="F36" t="n">
-        <v>238.24236806254</v>
+        <v>44.88</v>
       </c>
       <c r="G36" t="n">
-        <v>238.24236806254</v>
+        <v>44.88</v>
       </c>
       <c r="H36" t="n">
-        <v>238.24236806254</v>
+        <v>44.88</v>
       </c>
       <c r="I36" t="n">
         <v>44.88</v>
@@ -7019,40 +7019,40 @@
         <v>1252.251891400195</v>
       </c>
       <c r="N36" t="n">
-        <v>1575.521778846774</v>
+        <v>1575.521778846848</v>
       </c>
       <c r="O36" t="n">
-        <v>1990.370569304078</v>
+        <v>1990.370569304152</v>
       </c>
       <c r="P36" t="n">
-        <v>2244</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="Q36" t="n">
-        <v>2244</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="R36" t="n">
-        <v>2086.491990537524</v>
+        <v>2086.491990537597</v>
       </c>
       <c r="S36" t="n">
-        <v>1977.703740144454</v>
+        <v>1900.680701998215</v>
       </c>
       <c r="T36" t="n">
-        <v>1919.775113185654</v>
+        <v>1842.752075039415</v>
       </c>
       <c r="U36" t="n">
-        <v>1864.056672795147</v>
+        <v>1787.033634648908</v>
       </c>
       <c r="V36" t="n">
-        <v>1793.843877652197</v>
+        <v>1716.820839505958</v>
       </c>
       <c r="W36" t="n">
-        <v>1705.58817774328</v>
+        <v>1628.565139597041</v>
       </c>
       <c r="X36" t="n">
-        <v>1629.969249010565</v>
+        <v>1204.461362379478</v>
       </c>
       <c r="Y36" t="n">
-        <v>1226.543599751843</v>
+        <v>1149.520561605605</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>430.5948697912525</v>
+        <v>608.5605946885323</v>
       </c>
       <c r="C37" t="n">
-        <v>430.5948697912525</v>
+        <v>680.1126005069681</v>
       </c>
       <c r="D37" t="n">
-        <v>430.5948697912525</v>
+        <v>738.9817446319681</v>
       </c>
       <c r="E37" t="n">
-        <v>493.9737740026656</v>
+        <v>802.3606488433811</v>
       </c>
       <c r="F37" t="n">
-        <v>563.884746594601</v>
+        <v>872.2716214353167</v>
       </c>
       <c r="G37" t="n">
-        <v>663.4607928093551</v>
+        <v>971.8476676500708</v>
       </c>
       <c r="H37" t="n">
-        <v>784.0351212474412</v>
+        <v>1092.421996088157</v>
       </c>
       <c r="I37" t="n">
-        <v>936.1843379750594</v>
+        <v>1277.734337975059</v>
       </c>
       <c r="J37" t="n">
         <v>1286.615337807839</v>
@@ -7119,19 +7119,19 @@
         <v>181.1525496506081</v>
       </c>
       <c r="U37" t="n">
-        <v>373.2875321249604</v>
+        <v>280.272247059337</v>
       </c>
       <c r="V37" t="n">
-        <v>373.2875321249604</v>
+        <v>280.272247059337</v>
       </c>
       <c r="W37" t="n">
-        <v>373.2875321249604</v>
+        <v>397.7131653190144</v>
       </c>
       <c r="X37" t="n">
-        <v>373.2875321249604</v>
+        <v>494.2939563432079</v>
       </c>
       <c r="Y37" t="n">
-        <v>373.2875321249604</v>
+        <v>551.2532570222402</v>
       </c>
     </row>
     <row r="38">
@@ -7141,40 +7141,40 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>444.0238605876006</v>
+        <v>439.3918839656581</v>
       </c>
       <c r="C38" t="n">
-        <v>338.4939835744754</v>
+        <v>333.8620069525329</v>
       </c>
       <c r="D38" t="n">
-        <v>272.4948363625059</v>
+        <v>267.8628597405634</v>
       </c>
       <c r="E38" t="n">
-        <v>212.531917567689</v>
+        <v>207.8999409457465</v>
       </c>
       <c r="F38" t="n">
-        <v>152.0373431151518</v>
+        <v>147.4053664932093</v>
       </c>
       <c r="G38" t="n">
-        <v>94.09552754682417</v>
+        <v>89.46355092488167</v>
       </c>
       <c r="H38" t="n">
-        <v>44.8799999999892</v>
+        <v>44.88</v>
       </c>
       <c r="I38" t="n">
         <v>44.88</v>
       </c>
       <c r="J38" t="n">
-        <v>553.4018942939372</v>
+        <v>127.400205073642</v>
       </c>
       <c r="K38" t="n">
-        <v>729.0734691180577</v>
+        <v>553.8331213236512</v>
       </c>
       <c r="L38" t="n">
-        <v>947.0095916306205</v>
+        <v>771.7692438362141</v>
       </c>
       <c r="M38" t="n">
-        <v>1502.399591630621</v>
+        <v>1327.159243836214</v>
       </c>
       <c r="N38" t="n">
         <v>1882.549243836214</v>
@@ -7189,28 +7189,28 @@
         <v>2244</v>
       </c>
       <c r="R38" t="n">
-        <v>2244.000000000077</v>
+        <v>2244.000000000059</v>
       </c>
       <c r="S38" t="n">
-        <v>2129.379271720411</v>
+        <v>2124.747295098468</v>
       </c>
       <c r="T38" t="n">
-        <v>1891.430706855763</v>
+        <v>1886.798730233821</v>
       </c>
       <c r="U38" t="n">
-        <v>1584.249193160146</v>
+        <v>1579.617216538204</v>
       </c>
       <c r="V38" t="n">
-        <v>1296.52088592093</v>
+        <v>1291.888909298988</v>
       </c>
       <c r="W38" t="n">
-        <v>1000.184041495731</v>
+        <v>995.5520648737879</v>
       </c>
       <c r="X38" t="n">
-        <v>750.4044117374804</v>
+        <v>745.7724351155377</v>
       </c>
       <c r="Y38" t="n">
-        <v>582.4070049871708</v>
+        <v>577.7750283652283</v>
       </c>
     </row>
     <row r="39">
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64.1098983264868</v>
+        <v>1101.795089801022</v>
       </c>
       <c r="C39" t="n">
-        <v>47.84736050272993</v>
+        <v>1085.532551977265</v>
       </c>
       <c r="D39" t="n">
-        <v>44.88</v>
+        <v>734.0803429896864</v>
       </c>
       <c r="E39" t="n">
-        <v>44.88</v>
+        <v>387.9469114524009</v>
       </c>
       <c r="F39" t="n">
         <v>44.88</v>
@@ -7250,46 +7250,46 @@
         <v>547.1588055149654</v>
       </c>
       <c r="L39" t="n">
-        <v>976.7579942888765</v>
+        <v>976.7579942888583</v>
       </c>
       <c r="M39" t="n">
-        <v>1250.062386031736</v>
+        <v>1250.062386031718</v>
       </c>
       <c r="N39" t="n">
-        <v>1575.521778846851</v>
+        <v>1575.521778846833</v>
       </c>
       <c r="O39" t="n">
-        <v>1990.370569304155</v>
+        <v>1990.370569304137</v>
       </c>
       <c r="P39" t="n">
-        <v>2244.000000000077</v>
+        <v>2244.000000000059</v>
       </c>
       <c r="Q39" t="n">
-        <v>2166.976961853761</v>
+        <v>2244.000000000059</v>
       </c>
       <c r="R39" t="n">
-        <v>2009.468952391285</v>
+        <v>2086.491990537583</v>
       </c>
       <c r="S39" t="n">
-        <v>1900.680701998215</v>
+        <v>1977.703740144512</v>
       </c>
       <c r="T39" t="n">
-        <v>1842.752075039415</v>
+        <v>1919.775113185713</v>
       </c>
       <c r="U39" t="n">
-        <v>1438.54878616406</v>
+        <v>1864.056672795206</v>
       </c>
       <c r="V39" t="n">
-        <v>1019.851142536262</v>
+        <v>1793.843877652256</v>
       </c>
       <c r="W39" t="n">
-        <v>583.1105941424954</v>
+        <v>1620.79578561703</v>
       </c>
       <c r="X39" t="n">
-        <v>159.0068169249322</v>
+        <v>1196.692008399467</v>
       </c>
       <c r="Y39" t="n">
-        <v>104.0660161510591</v>
+        <v>1141.751207625594</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>447.8624118438701</v>
+        <v>845.9472726401018</v>
       </c>
       <c r="C40" t="n">
-        <v>466.4493852635086</v>
+        <v>917.4992784585376</v>
       </c>
       <c r="D40" t="n">
-        <v>525.3185293885086</v>
+        <v>917.4992784585376</v>
       </c>
       <c r="E40" t="n">
-        <v>588.6974335999216</v>
+        <v>980.8781826699505</v>
       </c>
       <c r="F40" t="n">
-        <v>658.6084061918571</v>
+        <v>1050.789155261886</v>
       </c>
       <c r="G40" t="n">
-        <v>758.1844524066112</v>
+        <v>1150.36520147664</v>
       </c>
       <c r="H40" t="n">
-        <v>878.7587808446973</v>
+        <v>1270.939529914726</v>
       </c>
       <c r="I40" t="n">
-        <v>1064.0711227316</v>
+        <v>1405.6211227316</v>
       </c>
       <c r="J40" t="n">
         <v>1414.502122564379</v>
@@ -7353,22 +7353,22 @@
         <v>44.88</v>
       </c>
       <c r="T40" t="n">
-        <v>44.88</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="U40" t="n">
-        <v>237.0149824743522</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="V40" t="n">
-        <v>237.0149824743522</v>
+        <v>517.6589250109064</v>
       </c>
       <c r="W40" t="n">
-        <v>237.0149824743522</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="X40" t="n">
-        <v>333.5957734985457</v>
+        <v>731.6806342947774</v>
       </c>
       <c r="Y40" t="n">
-        <v>390.555074177578</v>
+        <v>788.6399349738097</v>
       </c>
     </row>
     <row r="41">
@@ -7393,7 +7393,7 @@
         <v>147.4053664931506</v>
       </c>
       <c r="G41" t="n">
-        <v>94.09552754683497</v>
+        <v>89.46355092482304</v>
       </c>
       <c r="H41" t="n">
         <v>44.88</v>
@@ -7408,19 +7408,19 @@
         <v>303.0717798977627</v>
       </c>
       <c r="L41" t="n">
-        <v>521.0079024103255</v>
+        <v>771.7692438362141</v>
       </c>
       <c r="M41" t="n">
-        <v>1076.397902410326</v>
+        <v>1327.159243836214</v>
       </c>
       <c r="N41" t="n">
-        <v>1631.787902410325</v>
+        <v>1882.549243836214</v>
       </c>
       <c r="O41" t="n">
-        <v>1794.929708667652</v>
+        <v>2045.691050093541</v>
       </c>
       <c r="P41" t="n">
-        <v>1993.238658574111</v>
+        <v>2244</v>
       </c>
       <c r="Q41" t="n">
         <v>2244</v>
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>411.0270273858001</v>
+        <v>64.1098983264868</v>
       </c>
       <c r="C42" t="n">
-        <v>394.7644895620432</v>
+        <v>47.84736050272993</v>
       </c>
       <c r="D42" t="n">
-        <v>391.7971290593132</v>
+        <v>44.88</v>
       </c>
       <c r="E42" t="n">
-        <v>391.7971290593132</v>
+        <v>44.88</v>
       </c>
       <c r="F42" t="n">
-        <v>391.7971290593132</v>
+        <v>44.88</v>
       </c>
       <c r="G42" t="n">
-        <v>63.52121136584174</v>
+        <v>44.88</v>
       </c>
       <c r="H42" t="n">
-        <v>63.52121136584174</v>
+        <v>44.88</v>
       </c>
       <c r="I42" t="n">
         <v>44.88</v>
@@ -7493,40 +7493,40 @@
         <v>1252.251891400195</v>
       </c>
       <c r="N42" t="n">
-        <v>1575.521778846859</v>
+        <v>1575.52177884684</v>
       </c>
       <c r="O42" t="n">
-        <v>1990.370569304162</v>
+        <v>1990.370569304144</v>
       </c>
       <c r="P42" t="n">
-        <v>2244.000000000084</v>
+        <v>2244.000000000066</v>
       </c>
       <c r="Q42" t="n">
-        <v>2165.409242428226</v>
+        <v>2166.976961853761</v>
       </c>
       <c r="R42" t="n">
-        <v>2007.90123296575</v>
+        <v>2009.468952391285</v>
       </c>
       <c r="S42" t="n">
-        <v>1550.628134087831</v>
+        <v>1900.680701998215</v>
       </c>
       <c r="T42" t="n">
-        <v>1492.699507129031</v>
+        <v>1842.752075039415</v>
       </c>
       <c r="U42" t="n">
-        <v>1088.496218253676</v>
+        <v>1787.033634648908</v>
       </c>
       <c r="V42" t="n">
-        <v>1018.283423110726</v>
+        <v>1716.820839505959</v>
       </c>
       <c r="W42" t="n">
-        <v>930.0277232018087</v>
+        <v>1280.080291112193</v>
       </c>
       <c r="X42" t="n">
-        <v>505.9239459842455</v>
+        <v>855.9765138946293</v>
       </c>
       <c r="Y42" t="n">
-        <v>450.9831452103724</v>
+        <v>452.5508646359077</v>
       </c>
     </row>
     <row r="43">
@@ -7536,34 +7536,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>622.8982726483962</v>
+        <v>741.8504714918809</v>
       </c>
       <c r="C43" t="n">
-        <v>694.4502784668319</v>
+        <v>813.4024773103166</v>
       </c>
       <c r="D43" t="n">
-        <v>753.319422591832</v>
+        <v>872.2716214353167</v>
       </c>
       <c r="E43" t="n">
-        <v>816.698326803245</v>
+        <v>872.2716214353167</v>
       </c>
       <c r="F43" t="n">
-        <v>886.6092993951805</v>
+        <v>872.2716214353167</v>
       </c>
       <c r="G43" t="n">
-        <v>986.1853456099346</v>
+        <v>971.8476676500708</v>
       </c>
       <c r="H43" t="n">
-        <v>1106.759674048021</v>
+        <v>1092.421996088157</v>
       </c>
       <c r="I43" t="n">
-        <v>1292.072015934923</v>
+        <v>1277.734337975059</v>
       </c>
       <c r="J43" t="n">
-        <v>1300.953015767703</v>
+        <v>1286.615337807839</v>
       </c>
       <c r="K43" t="n">
-        <v>1428.839800524243</v>
+        <v>1414.502122564379</v>
       </c>
       <c r="L43" t="n">
         <v>1428.839800524243</v>
@@ -7584,7 +7584,7 @@
         <v>408.4509731532439</v>
       </c>
       <c r="R43" t="n">
-        <v>51.41391723586987</v>
+        <v>51.41391723586989</v>
       </c>
       <c r="S43" t="n">
         <v>44.88</v>
@@ -7596,16 +7596,16 @@
         <v>373.2875321249604</v>
       </c>
       <c r="V43" t="n">
-        <v>373.2875321249604</v>
+        <v>517.6589250109064</v>
       </c>
       <c r="W43" t="n">
-        <v>490.7284503846378</v>
+        <v>587.9623428013952</v>
       </c>
       <c r="X43" t="n">
-        <v>508.6316343030718</v>
+        <v>684.5431338255887</v>
       </c>
       <c r="Y43" t="n">
-        <v>565.590934982104</v>
+        <v>684.5431338255887</v>
       </c>
     </row>
     <row r="44">
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>444.0238605876114</v>
+        <v>439.3918839655994</v>
       </c>
       <c r="C44" t="n">
-        <v>338.4939835744862</v>
+        <v>333.8620069524742</v>
       </c>
       <c r="D44" t="n">
-        <v>272.4948363625167</v>
+        <v>267.8628597405047</v>
       </c>
       <c r="E44" t="n">
-        <v>212.5319175676998</v>
+        <v>207.8999409456879</v>
       </c>
       <c r="F44" t="n">
-        <v>152.0373431151626</v>
+        <v>147.4053664931506</v>
       </c>
       <c r="G44" t="n">
         <v>94.09552754683497</v>
@@ -7648,16 +7648,16 @@
         <v>521.0079024103255</v>
       </c>
       <c r="M44" t="n">
-        <v>1076.397902410326</v>
+        <v>521.0079024103255</v>
       </c>
       <c r="N44" t="n">
-        <v>1631.787902410325</v>
+        <v>970.0781937426734</v>
       </c>
       <c r="O44" t="n">
-        <v>1794.929708667652</v>
+        <v>1133.22</v>
       </c>
       <c r="P44" t="n">
-        <v>1993.238658574111</v>
+        <v>1688.61</v>
       </c>
       <c r="Q44" t="n">
         <v>2244</v>
@@ -7666,25 +7666,25 @@
         <v>2244</v>
       </c>
       <c r="S44" t="n">
-        <v>2129.379271720421</v>
+        <v>2124.74729509841</v>
       </c>
       <c r="T44" t="n">
-        <v>1891.430706855774</v>
+        <v>1886.798730233762</v>
       </c>
       <c r="U44" t="n">
-        <v>1584.249193160157</v>
+        <v>1579.617216538145</v>
       </c>
       <c r="V44" t="n">
-        <v>1296.520885920941</v>
+        <v>1291.888909298929</v>
       </c>
       <c r="W44" t="n">
-        <v>1000.184041495741</v>
+        <v>995.5520648737293</v>
       </c>
       <c r="X44" t="n">
-        <v>750.404411737491</v>
+        <v>745.7724351154791</v>
       </c>
       <c r="Y44" t="n">
-        <v>582.4070049871816</v>
+        <v>577.7750283651696</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>257.4722663890267</v>
+        <v>64.1098983264868</v>
       </c>
       <c r="C45" t="n">
-        <v>241.2097285652699</v>
+        <v>47.84736050272993</v>
       </c>
       <c r="D45" t="n">
-        <v>238.24236806254</v>
+        <v>44.88</v>
       </c>
       <c r="E45" t="n">
-        <v>238.24236806254</v>
+        <v>44.88</v>
       </c>
       <c r="F45" t="n">
-        <v>238.24236806254</v>
+        <v>44.88</v>
       </c>
       <c r="G45" t="n">
-        <v>238.24236806254</v>
+        <v>44.88</v>
       </c>
       <c r="H45" t="n">
-        <v>238.24236806254</v>
+        <v>44.88</v>
       </c>
       <c r="I45" t="n">
         <v>44.88</v>
@@ -7724,7 +7724,7 @@
         <v>547.1588055149654</v>
       </c>
       <c r="L45" t="n">
-        <v>976.7579942887996</v>
+        <v>978.9474996573354</v>
       </c>
       <c r="M45" t="n">
         <v>1250.062386031659</v>
@@ -7739,31 +7739,31 @@
         <v>2244</v>
       </c>
       <c r="Q45" t="n">
-        <v>2244</v>
+        <v>2166.976961853761</v>
       </c>
       <c r="R45" t="n">
-        <v>1738.007142052676</v>
+        <v>1660.984103906437</v>
       </c>
       <c r="S45" t="n">
-        <v>1629.218891659606</v>
+        <v>1552.195853513367</v>
       </c>
       <c r="T45" t="n">
-        <v>1571.290264700806</v>
+        <v>1494.267226554567</v>
       </c>
       <c r="U45" t="n">
-        <v>1283.426305741751</v>
+        <v>1438.54878616406</v>
       </c>
       <c r="V45" t="n">
-        <v>1213.213510598802</v>
+        <v>1019.851142536262</v>
       </c>
       <c r="W45" t="n">
-        <v>1124.957810689884</v>
+        <v>583.1105941424954</v>
       </c>
       <c r="X45" t="n">
-        <v>700.8540334723207</v>
+        <v>159.0068169249322</v>
       </c>
       <c r="Y45" t="n">
-        <v>297.4283842135991</v>
+        <v>104.0660161510591</v>
       </c>
     </row>
     <row r="46">
@@ -7773,34 +7773,34 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>394.8973794450728</v>
+        <v>845.9472726401018</v>
       </c>
       <c r="C46" t="n">
-        <v>466.4493852635086</v>
+        <v>917.4992784585376</v>
       </c>
       <c r="D46" t="n">
-        <v>525.3185293885086</v>
+        <v>976.3684225835376</v>
       </c>
       <c r="E46" t="n">
-        <v>588.6974335999216</v>
+        <v>1039.747326794951</v>
       </c>
       <c r="F46" t="n">
-        <v>658.6084061918571</v>
+        <v>1039.747326794951</v>
       </c>
       <c r="G46" t="n">
-        <v>758.1844524066112</v>
+        <v>1039.747326794951</v>
       </c>
       <c r="H46" t="n">
-        <v>878.7587808446973</v>
+        <v>1160.321655233037</v>
       </c>
       <c r="I46" t="n">
-        <v>1064.0711227316</v>
+        <v>1345.633997119939</v>
       </c>
       <c r="J46" t="n">
-        <v>1414.502122564379</v>
+        <v>1354.514996952718</v>
       </c>
       <c r="K46" t="n">
-        <v>1414.502122564379</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="L46" t="n">
         <v>1428.839800524243</v>
@@ -7827,22 +7827,22 @@
         <v>44.88</v>
       </c>
       <c r="T46" t="n">
-        <v>44.88</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="U46" t="n">
-        <v>184.0499500755549</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="V46" t="n">
-        <v>184.0499500755549</v>
+        <v>517.6589250109064</v>
       </c>
       <c r="W46" t="n">
-        <v>184.0499500755549</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="X46" t="n">
-        <v>280.6307410997484</v>
+        <v>731.6806342947774</v>
       </c>
       <c r="Y46" t="n">
-        <v>337.5900417787807</v>
+        <v>788.6399349738097</v>
       </c>
     </row>
   </sheetData>
@@ -7967,16 +7967,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>181.5167089435051</v>
       </c>
       <c r="L2" t="n">
-        <v>181.5167089435048</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>845.554996989051</v>
+        <v>845.5549969890513</v>
       </c>
       <c r="N2" t="n">
-        <v>777.3653500296342</v>
+        <v>777.3653500296346</v>
       </c>
       <c r="O2" t="n">
         <v>0.4816735941929551</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.1077446289929</v>
+        <v>502.1077446289934</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,16 +8204,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321.3286984924623</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>181.5167089435051</v>
       </c>
       <c r="M5" t="n">
-        <v>845.554996989051</v>
+        <v>845.5549969890513</v>
       </c>
       <c r="N5" t="n">
-        <v>777.3653500296342</v>
+        <v>777.3653500296346</v>
       </c>
       <c r="O5" t="n">
         <v>0.4816735941929551</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>362.2957550800353</v>
+        <v>502.1077446289934</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,16 +8441,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>321.3286984924627</v>
       </c>
       <c r="L8" t="n">
-        <v>181.5167089435048</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>845.554996989051</v>
+        <v>845.5549969890513</v>
       </c>
       <c r="N8" t="n">
-        <v>777.3653500296342</v>
+        <v>637.553360480677</v>
       </c>
       <c r="O8" t="n">
         <v>0.4816735941929551</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.1077446289929</v>
+        <v>502.1077446289934</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>427.8625025125627</v>
+        <v>248.1154848729378</v>
       </c>
       <c r="M11" t="n">
-        <v>947.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N11" t="n">
-        <v>872.2567340393384</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>447.6879293874177</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,13 +8918,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>427.8625025125627</v>
+        <v>423.7791327534173</v>
       </c>
       <c r="M14" t="n">
-        <v>943.2333759736296</v>
+        <v>947.3167457327731</v>
       </c>
       <c r="N14" t="n">
-        <v>876.3401037984784</v>
+        <v>876.340103798482</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9152,22 +9152,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>423.7791327534228</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>947.3167457327697</v>
+        <v>947.3167457327741</v>
       </c>
       <c r="N17" t="n">
-        <v>876.3401037984784</v>
+        <v>876.3401037984829</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>423.7791327534158</v>
       </c>
       <c r="Q17" t="n">
         <v>22.18109136266131</v>
@@ -9395,13 +9395,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>947.3167457327697</v>
+        <v>511.9098632833498</v>
       </c>
       <c r="N20" t="n">
-        <v>276.1435180588324</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>483.2102967097752</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -9629,19 +9629,19 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>427.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>947.3167457327697</v>
+        <v>923.4079490987783</v>
       </c>
       <c r="N23" t="n">
-        <v>872.2567340393384</v>
+        <v>876.3401037984788</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>447.6879293874155</v>
       </c>
       <c r="Q23" t="n">
         <v>22.18109136266131</v>
@@ -9863,16 +9863,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>471.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>425.7387287130186</v>
       </c>
       <c r="M26" t="n">
-        <v>948.3167457327706</v>
+        <v>948.3167457327695</v>
       </c>
       <c r="N26" t="n">
-        <v>237.8538857804631</v>
+        <v>877.3401037984784</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>425.738728713013</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>948.3167457327725</v>
+        <v>780.384492538876</v>
       </c>
       <c r="N29" t="n">
-        <v>877.3401037984811</v>
+        <v>877.3401037984784</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,22 +10334,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>471.5539648241206</v>
       </c>
       <c r="L32" t="n">
-        <v>160.2236954170817</v>
+        <v>428.8625025125627</v>
       </c>
       <c r="M32" t="n">
-        <v>299.3167457327696</v>
+        <v>948.3167457327695</v>
       </c>
       <c r="N32" t="n">
-        <v>877.3401037984829</v>
+        <v>402.6623651748138</v>
       </c>
       <c r="O32" t="n">
-        <v>484.2102967097754</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -10574,25 +10574,25 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>383.5539648241206</v>
       </c>
       <c r="L35" t="n">
-        <v>340.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>376.5382307790105</v>
+        <v>860.3167457327697</v>
       </c>
       <c r="N35" t="n">
-        <v>228.3401037984784</v>
+        <v>298.3924938555171</v>
       </c>
       <c r="O35" t="n">
-        <v>396.2102967097708</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>360.6879293874151</v>
       </c>
       <c r="Q35" t="n">
-        <v>583.1810913626613</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10662,7 +10662,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>483.1969055869708</v>
+        <v>483.1969055870447</v>
       </c>
       <c r="O36" t="n">
         <v>382.6817988009037</v>
@@ -10808,10 +10808,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>253.2942842685744</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
         <v>860.3167457327697</v>
       </c>
       <c r="N38" t="n">
-        <v>612.329651480896</v>
+        <v>789.3401037984784</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10893,7 +10893,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>385.8777148754963</v>
+        <v>385.8777148754779</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -11051,7 +11051,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>253.2942842685743</v>
       </c>
       <c r="M41" t="n">
         <v>860.3167457327697</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>275.4753756312358</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11136,7 +11136,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
-        <v>483.1969055870558</v>
+        <v>483.1969055870375</v>
       </c>
       <c r="O42" t="n">
         <v>382.6817988009037</v>
@@ -11291,19 +11291,19 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>860.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N44" t="n">
-        <v>789.3401037984784</v>
+        <v>681.946458679638</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>360.6879293874151</v>
       </c>
       <c r="Q44" t="n">
-        <v>275.4753756312358</v>
+        <v>583.1810913626613</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11367,10 +11367,10 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>385.8777148754186</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M45" t="n">
-        <v>471.6948204301074</v>
+        <v>469.483198845728</v>
       </c>
       <c r="N45" t="n">
         <v>485.4085271713503</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.596816457606004e-12</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.956056855789967</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23286,7 +23286,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.956056855791644</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -23478,7 +23478,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2.956056855769603</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.956056855791758</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23697,7 +23697,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.956056855791587</v>
+        <v>2.956056855789797</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -23952,7 +23952,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.956056855770285</v>
+        <v>2.956056855756813</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.956056855789868</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.956056855791758</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -25119,7 +25119,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4.585656855791683</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>4.585656855791804</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25374,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>4.58565685573376</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4.585656855704514</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25608,10 +25608,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>4.585656855791843</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>4.585656855791797</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25845,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>4.585656855791843</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -25881,7 +25881,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>4.585656855791399</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3245404.164969369</v>
+        <v>3245404.16496937</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4032367.751348666</v>
+        <v>4032367.751348668</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4819331.337727963</v>
+        <v>4819331.337727964</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5606294.924107257</v>
+        <v>5606294.924107259</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6393258.51048655</v>
+        <v>6393258.510486552</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7180463.715845933</v>
+        <v>7180463.715845935</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7967574.366053802</v>
+        <v>7967574.366053804</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8754685.016261676</v>
+        <v>8754685.016261678</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9533218.544881091</v>
+        <v>9533218.544881094</v>
       </c>
     </row>
     <row r="14">
@@ -26281,19 +26281,19 @@
         <v>1416534.455482733</v>
       </c>
       <c r="F2" t="n">
-        <v>1416534.455482733</v>
+        <v>1416534.455482736</v>
       </c>
       <c r="G2" t="n">
-        <v>1416534.455482733</v>
+        <v>1416534.455482734</v>
       </c>
       <c r="H2" t="n">
-        <v>1416534.455482734</v>
+        <v>1416534.455482736</v>
       </c>
       <c r="I2" t="n">
         <v>1416534.455482733</v>
       </c>
       <c r="J2" t="n">
-        <v>1416799.170374169</v>
+        <v>1416799.17037417</v>
       </c>
       <c r="K2" t="n">
         <v>1416799.170374169</v>
@@ -26305,10 +26305,10 @@
         <v>1416388.524802734</v>
       </c>
       <c r="N2" t="n">
-        <v>1416388.524802741</v>
+        <v>1416388.524802739</v>
       </c>
       <c r="O2" t="n">
-        <v>1416388.524802733</v>
+        <v>1416388.524802734</v>
       </c>
       <c r="P2" t="n">
         <v>1416388.524802733</v>
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>232073</v>
+        <v>232073.0000000001</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602166.8573620638</v>
+        <v>601967.7658514545</v>
       </c>
       <c r="C4" t="n">
-        <v>600158.4933044577</v>
+        <v>599959.4017938485</v>
       </c>
       <c r="D4" t="n">
-        <v>598147.4047756541</v>
+        <v>597948.3132650447</v>
       </c>
       <c r="E4" t="n">
-        <v>513949.0290844531</v>
+        <v>513751.7523916514</v>
       </c>
       <c r="F4" t="n">
-        <v>512264.4313324891</v>
+        <v>512067.1546396881</v>
       </c>
       <c r="G4" t="n">
-        <v>510577.5088988312</v>
+        <v>510380.2322060294</v>
       </c>
       <c r="H4" t="n">
-        <v>508888.2451130991</v>
+        <v>508690.9684202978</v>
       </c>
       <c r="I4" t="n">
-        <v>507196.6230877017</v>
+        <v>506999.3463949</v>
       </c>
       <c r="J4" t="n">
-        <v>505559.8209559915</v>
+        <v>505362.3521738978</v>
       </c>
       <c r="K4" t="n">
-        <v>503863.6019243026</v>
+        <v>503666.133142209</v>
       </c>
       <c r="L4" t="n">
-        <v>502164.9728882493</v>
+        <v>501967.5041061556</v>
       </c>
       <c r="M4" t="n">
-        <v>506489.4162279241</v>
+        <v>506308.908453467</v>
       </c>
       <c r="N4" t="n">
-        <v>504723.3213042096</v>
+        <v>504542.8135297522</v>
       </c>
       <c r="O4" t="n">
-        <v>502954.6717247888</v>
+        <v>502774.1639503328</v>
       </c>
       <c r="P4" t="n">
-        <v>501183.4482814748</v>
+        <v>501002.9405070185</v>
       </c>
     </row>
     <row r="5">
@@ -26425,28 +26425,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58612.2</v>
+        <v>58612.20000000003</v>
       </c>
       <c r="C5" t="n">
-        <v>58612.2</v>
+        <v>58612.20000000003</v>
       </c>
       <c r="D5" t="n">
-        <v>58612.2</v>
+        <v>58612.20000000003</v>
       </c>
       <c r="E5" t="n">
-        <v>73949.149</v>
+        <v>73949.14900000003</v>
       </c>
       <c r="F5" t="n">
-        <v>73949.149</v>
+        <v>73949.14900000003</v>
       </c>
       <c r="G5" t="n">
-        <v>73949.149</v>
+        <v>73949.14900000003</v>
       </c>
       <c r="H5" t="n">
-        <v>73949.149</v>
+        <v>73949.14900000003</v>
       </c>
       <c r="I5" t="n">
-        <v>73949.149</v>
+        <v>73949.14900000003</v>
       </c>
       <c r="J5" t="n">
         <v>74009.94899999999</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>523947.1130121052</v>
+        <v>524146.2045227143</v>
       </c>
       <c r="C6" t="n">
-        <v>758028.4770697113</v>
+        <v>758227.5685803207</v>
       </c>
       <c r="D6" t="n">
-        <v>760039.565598515</v>
+        <v>760238.6571091242</v>
       </c>
       <c r="E6" t="n">
-        <v>237488.2773982801</v>
+        <v>237685.5540910818</v>
       </c>
       <c r="F6" t="n">
-        <v>830320.8751502442</v>
+        <v>830518.1518430475</v>
       </c>
       <c r="G6" t="n">
-        <v>832007.797583902</v>
+        <v>832205.0742767043</v>
       </c>
       <c r="H6" t="n">
-        <v>833697.0613696354</v>
+        <v>833894.3380624384</v>
       </c>
       <c r="I6" t="n">
-        <v>835388.6833950315</v>
+        <v>835585.9600878335</v>
       </c>
       <c r="J6" t="n">
-        <v>448429.4004181781</v>
+        <v>448626.8692002719</v>
       </c>
       <c r="K6" t="n">
-        <v>838925.6194498668</v>
+        <v>839123.0882319604</v>
       </c>
       <c r="L6" t="n">
-        <v>840624.2484859201</v>
+        <v>840821.7172680139</v>
       </c>
       <c r="M6" t="n">
-        <v>754549.9035748104</v>
+        <v>754730.4113492668</v>
       </c>
       <c r="N6" t="n">
-        <v>840987.9984985311</v>
+        <v>841168.5062729869</v>
       </c>
       <c r="O6" t="n">
-        <v>585956.6480779439</v>
+        <v>586137.1558524009</v>
       </c>
       <c r="P6" t="n">
-        <v>844527.8715212586</v>
+        <v>844708.379295715</v>
       </c>
     </row>
   </sheetData>
@@ -26859,28 +26859,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="C4" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="D4" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="E4" t="n">
-        <v>648</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="F4" t="n">
-        <v>648</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="G4" t="n">
-        <v>648</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="H4" t="n">
-        <v>648</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="I4" t="n">
-        <v>648</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="J4" t="n">
         <v>649</v>
@@ -26984,10 +26984,10 @@
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -26999,7 +26999,7 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27317,7 +27317,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -27448,7 +27448,7 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>398.046593539207</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
         <v>400</v>
@@ -27484,7 +27484,7 @@
         <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>398.0465935392069</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,10 +27512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>268.6337901446168</v>
+        <v>10.55655664632621</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>275.0857779292421</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27566,19 +27566,19 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>30.46477465147569</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>45.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27597,10 +27597,10 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
@@ -27609,19 +27609,19 @@
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>353.5969747562122</v>
+        <v>396.1372930982033</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>395.9334970102382</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,22 +27642,22 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1365780635112</v>
+        <v>372.1857232844806</v>
       </c>
       <c r="T4" t="n">
         <v>209.2309599488807</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.0465935392086</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857107</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27752,22 +27752,22 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>207.4990601318526</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0284079411381</v>
+        <v>12.72239498288104</v>
       </c>
       <c r="I6" t="n">
         <v>209.4985557026693</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>26.19578428848826</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27828,13 +27828,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>294.3826718271957</v>
       </c>
       <c r="E7" t="n">
         <v>280.9809048369565</v>
@@ -27846,16 +27846,16 @@
         <v>244.858135136612</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J7" t="n">
         <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
         <v>395.9334970102382</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
@@ -27894,10 +27894,10 @@
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>267.5144707406857</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>132.1643059857123</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>398.0465935392069</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>259.0356047226625</v>
+        <v>73.64590163346838</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -28004,10 +28004,10 @@
         <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28052,10 +28052,10 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>45.86273944538715</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.39139276613437</v>
+        <v>25.39139276613395</v>
       </c>
     </row>
     <row r="10">
@@ -28065,13 +28065,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
@@ -28080,22 +28080,22 @@
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>375.2887696291973</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.047816275856</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
-        <v>266.941429538848</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>395.9334970102382</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2309599488807</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9482601269169</v>
+        <v>349.819676270712</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28226,7 +28226,7 @@
         <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>321</v>
@@ -28238,13 +28238,13 @@
         <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28274,7 +28274,7 @@
         <v>321</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28286,7 +28286,7 @@
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>8.269477602770735</v>
+        <v>321</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -28323,7 +28323,7 @@
         <v>321</v>
       </c>
       <c r="I13" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="J13" t="n">
         <v>321</v>
@@ -28356,7 +28356,7 @@
         <v>321</v>
       </c>
       <c r="T13" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="U13" t="n">
         <v>321</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083760538</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28466,19 +28466,19 @@
         <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>321</v>
+        <v>215.6455832169962</v>
       </c>
       <c r="I15" t="n">
         <v>191.4287443819146</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>321</v>
@@ -28520,16 +28520,16 @@
         <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>137.8407332208563</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
@@ -28542,16 +28542,16 @@
         <v>321</v>
       </c>
       <c r="C16" t="n">
+        <v>321</v>
+      </c>
+      <c r="D16" t="n">
+        <v>321</v>
+      </c>
+      <c r="E16" t="n">
+        <v>321</v>
+      </c>
+      <c r="F16" t="n">
         <v>315.8198010595347</v>
-      </c>
-      <c r="D16" t="n">
-        <v>321</v>
-      </c>
-      <c r="E16" t="n">
-        <v>321</v>
-      </c>
-      <c r="F16" t="n">
-        <v>321</v>
       </c>
       <c r="G16" t="n">
         <v>321</v>
@@ -28700,13 +28700,13 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>321</v>
@@ -28715,7 +28715,7 @@
         <v>321</v>
       </c>
       <c r="H18" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="I18" t="n">
         <v>191.4287443819146</v>
@@ -28754,16 +28754,16 @@
         <v>321</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>137.8407332208563</v>
+        <v>321</v>
       </c>
       <c r="Y18" t="n">
         <v>321</v>
@@ -28782,16 +28782,16 @@
         <v>321</v>
       </c>
       <c r="D19" t="n">
+        <v>321</v>
+      </c>
+      <c r="E19" t="n">
+        <v>321</v>
+      </c>
+      <c r="F19" t="n">
+        <v>321</v>
+      </c>
+      <c r="G19" t="n">
         <v>315.8198010595347</v>
-      </c>
-      <c r="E19" t="n">
-        <v>321</v>
-      </c>
-      <c r="F19" t="n">
-        <v>321</v>
-      </c>
-      <c r="G19" t="n">
-        <v>321</v>
       </c>
       <c r="H19" t="n">
         <v>321</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>163.2515083760547</v>
+        <v>163.2515083760667</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28982,25 +28982,25 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S21" t="n">
         <v>321</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>215.6455832169961</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>321</v>
+        <v>215.6455832169962</v>
       </c>
       <c r="Y21" t="n">
         <v>321</v>
@@ -29025,19 +29025,19 @@
         <v>321</v>
       </c>
       <c r="F22" t="n">
+        <v>321</v>
+      </c>
+      <c r="G22" t="n">
+        <v>321</v>
+      </c>
+      <c r="H22" t="n">
+        <v>321</v>
+      </c>
+      <c r="I22" t="n">
+        <v>321</v>
+      </c>
+      <c r="J22" t="n">
         <v>315.8198010595347</v>
-      </c>
-      <c r="G22" t="n">
-        <v>321</v>
-      </c>
-      <c r="H22" t="n">
-        <v>321</v>
-      </c>
-      <c r="I22" t="n">
-        <v>321</v>
-      </c>
-      <c r="J22" t="n">
-        <v>321</v>
       </c>
       <c r="K22" t="n">
         <v>321</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R24" t="n">
         <v>321</v>
@@ -29228,16 +29228,16 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>215.645583216996</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -29259,7 +29259,7 @@
         <v>321</v>
       </c>
       <c r="E25" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="F25" t="n">
         <v>321</v>
@@ -29304,7 +29304,7 @@
         <v>321</v>
       </c>
       <c r="T25" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="U25" t="n">
         <v>321</v>
@@ -29347,7 +29347,7 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>321</v>
+        <v>320.0752568557916</v>
       </c>
       <c r="I26" t="n">
         <v>96.3013908384635</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>321</v>
+        <v>215.6455832169962</v>
       </c>
       <c r="C27" t="n">
         <v>321</v>
@@ -29423,7 +29423,7 @@
         <v>321</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H27" t="n">
         <v>321</v>
@@ -29462,7 +29462,7 @@
         <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>215.6455832169963</v>
+        <v>321</v>
       </c>
       <c r="U27" t="n">
         <v>321</v>
@@ -29471,7 +29471,7 @@
         <v>321</v>
       </c>
       <c r="W27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -29511,40 +29511,40 @@
         <v>321</v>
       </c>
       <c r="J28" t="n">
+        <v>321</v>
+      </c>
+      <c r="K28" t="n">
+        <v>321</v>
+      </c>
+      <c r="L28" t="n">
+        <v>321</v>
+      </c>
+      <c r="M28" t="n">
+        <v>321</v>
+      </c>
+      <c r="N28" t="n">
+        <v>321</v>
+      </c>
+      <c r="O28" t="n">
+        <v>321</v>
+      </c>
+      <c r="P28" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>321</v>
+      </c>
+      <c r="R28" t="n">
+        <v>321</v>
+      </c>
+      <c r="S28" t="n">
+        <v>321</v>
+      </c>
+      <c r="T28" t="n">
+        <v>321</v>
+      </c>
+      <c r="U28" t="n">
         <v>315.8198010595347</v>
-      </c>
-      <c r="K28" t="n">
-        <v>321</v>
-      </c>
-      <c r="L28" t="n">
-        <v>321</v>
-      </c>
-      <c r="M28" t="n">
-        <v>321</v>
-      </c>
-      <c r="N28" t="n">
-        <v>321</v>
-      </c>
-      <c r="O28" t="n">
-        <v>321</v>
-      </c>
-      <c r="P28" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>321</v>
-      </c>
-      <c r="R28" t="n">
-        <v>321</v>
-      </c>
-      <c r="S28" t="n">
-        <v>321</v>
-      </c>
-      <c r="T28" t="n">
-        <v>321</v>
-      </c>
-      <c r="U28" t="n">
-        <v>321</v>
       </c>
       <c r="V28" t="n">
         <v>321</v>
@@ -29645,10 +29645,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="C30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -29657,13 +29657,13 @@
         <v>321</v>
       </c>
       <c r="F30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>137.8407332208564</v>
+        <v>321</v>
       </c>
       <c r="I30" t="n">
         <v>191.4287443819146</v>
@@ -29711,7 +29711,7 @@
         <v>321</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="n">
         <v>321</v>
@@ -29724,13 +29724,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="C31" t="n">
         <v>321</v>
       </c>
       <c r="D31" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="E31" t="n">
         <v>321</v>
@@ -29885,13 +29885,13 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
         <v>321</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F33" t="n">
         <v>321</v>
@@ -29942,13 +29942,13 @@
         <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="W33" t="n">
-        <v>137.8407332208565</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -29964,7 +29964,7 @@
         <v>321</v>
       </c>
       <c r="C34" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="D34" t="n">
         <v>321</v>
@@ -30018,7 +30018,7 @@
         <v>321</v>
       </c>
       <c r="U34" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="V34" t="n">
         <v>321</v>
@@ -30119,16 +30119,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>112.8480338390507</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -30140,7 +30140,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30170,7 +30170,7 @@
         <v>345</v>
       </c>
       <c r="S36" t="n">
-        <v>345</v>
+        <v>268.7471922351511</v>
       </c>
       <c r="T36" t="n">
         <v>345</v>
@@ -30185,10 +30185,10 @@
         <v>345</v>
       </c>
       <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
         <v>345</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30201,10 +30201,10 @@
         <v>345</v>
       </c>
       <c r="C37" t="n">
-        <v>272.7252466480447</v>
+        <v>345</v>
       </c>
       <c r="D37" t="n">
-        <v>285.5362180555555</v>
+        <v>345</v>
       </c>
       <c r="E37" t="n">
         <v>345</v>
@@ -30219,10 +30219,10 @@
         <v>345</v>
       </c>
       <c r="I37" t="n">
-        <v>311.5018937785006</v>
+        <v>345</v>
       </c>
       <c r="J37" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>345</v>
@@ -30255,19 +30255,19 @@
         <v>345</v>
       </c>
       <c r="U37" t="n">
-        <v>345</v>
+        <v>251.0451666003805</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>345</v>
       </c>
       <c r="X37" t="n">
-        <v>247.4436454301076</v>
+        <v>345</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
@@ -30298,7 +30298,7 @@
         <v>345</v>
       </c>
       <c r="I38" t="n">
-        <v>96.30139083847442</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.2515083761108</v>
+        <v>163.2515083760924</v>
       </c>
       <c r="S38" t="n">
         <v>345</v>
@@ -30362,13 +30362,13 @@
         <v>345</v>
       </c>
       <c r="D39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>324.9931585165368</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.552042231287416</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R39" t="n">
         <v>345</v>
@@ -30413,13 +30413,13 @@
         <v>345</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>261.0555317949551</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -30438,10 +30438,10 @@
         <v>345</v>
       </c>
       <c r="C40" t="n">
-        <v>291.4999672739421</v>
+        <v>345</v>
       </c>
       <c r="D40" t="n">
-        <v>345</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E40" t="n">
         <v>345</v>
@@ -30456,10 +30456,10 @@
         <v>345</v>
       </c>
       <c r="I40" t="n">
-        <v>345</v>
+        <v>293.8578292221931</v>
       </c>
       <c r="J40" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>215.821429538848</v>
@@ -30489,16 +30489,16 @@
         <v>345</v>
       </c>
       <c r="T40" t="n">
-        <v>207.3509599488807</v>
+        <v>345</v>
       </c>
       <c r="U40" t="n">
         <v>345</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>345</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>345</v>
       </c>
       <c r="X40" t="n">
         <v>345</v>
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>345</v>
@@ -30608,13 +30608,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H42" t="n">
         <v>324.959653224157</v>
       </c>
       <c r="I42" t="n">
-        <v>172.9739451297312</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,31 +30638,31 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1.55204223129823</v>
       </c>
       <c r="R42" t="n">
         <v>345</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="T42" t="n">
         <v>345</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="V42" t="n">
         <v>345</v>
       </c>
       <c r="W42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -30681,10 +30681,10 @@
         <v>345</v>
       </c>
       <c r="E43" t="n">
-        <v>345</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F43" t="n">
-        <v>345</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G43" t="n">
         <v>345</v>
@@ -30702,7 +30702,7 @@
         <v>345</v>
       </c>
       <c r="L43" t="n">
-        <v>330.5174970102382</v>
+        <v>345</v>
       </c>
       <c r="M43" t="n">
         <v>345</v>
@@ -30732,16 +30732,16 @@
         <v>345</v>
       </c>
       <c r="V43" t="n">
-        <v>199.1703102162162</v>
+        <v>345</v>
       </c>
       <c r="W43" t="n">
+        <v>297.3863631624357</v>
+      </c>
+      <c r="X43" t="n">
         <v>345</v>
       </c>
-      <c r="X43" t="n">
-        <v>265.5276695901419</v>
-      </c>
       <c r="Y43" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="44">
@@ -30851,7 +30851,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>77.80484999613995</v>
+        <v>1.552042231363501</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -30887,19 +30887,19 @@
         <v>345</v>
       </c>
       <c r="U45" t="n">
-        <v>115.175936617138</v>
+        <v>345</v>
       </c>
       <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
         <v>345</v>
-      </c>
-      <c r="W45" t="n">
-        <v>345</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -30921,10 +30921,10 @@
         <v>345</v>
       </c>
       <c r="F46" t="n">
-        <v>345</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G46" t="n">
-        <v>345</v>
+        <v>244.418135136612</v>
       </c>
       <c r="H46" t="n">
         <v>345</v>
@@ -30933,13 +30933,13 @@
         <v>345</v>
       </c>
       <c r="J46" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>215.821429538848</v>
+        <v>290.8969887020044</v>
       </c>
       <c r="L46" t="n">
-        <v>345</v>
+        <v>330.5174970102382</v>
       </c>
       <c r="M46" t="n">
         <v>345</v>
@@ -30963,16 +30963,16 @@
         <v>345</v>
       </c>
       <c r="T46" t="n">
-        <v>207.3509599488807</v>
+        <v>345</v>
       </c>
       <c r="U46" t="n">
-        <v>291.4999672739422</v>
+        <v>345</v>
       </c>
       <c r="V46" t="n">
-        <v>199.1703102162162</v>
+        <v>345</v>
       </c>
       <c r="W46" t="n">
-        <v>226.3728098387097</v>
+        <v>345</v>
       </c>
       <c r="X46" t="n">
         <v>345</v>
@@ -34746,16 +34746,16 @@
         <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
-        <v>52.67130150753769</v>
+        <v>234.1880104510428</v>
       </c>
       <c r="L2" t="n">
-        <v>246.8601159786807</v>
+        <v>65.34340703517586</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="N2" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34883,10 +34883,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -34895,19 +34895,19 @@
         <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
         <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>331.4596816580093</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="K4" t="n">
         <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.066502989761812</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>13.04914522096937</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34983,16 +34983,16 @@
         <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>65.34340703517591</v>
+        <v>246.8601159786809</v>
       </c>
       <c r="M5" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="N5" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35001,7 +35001,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>234.1880104510424</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,13 +35114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>8.846453771640212</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -35132,16 +35132,16 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8802509475617</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>228.952183724144</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T7" t="n">
         <v>190.7690400511193</v>
@@ -35180,10 +35180,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>20.07082531057817</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,16 +35220,16 @@
         <v>0.1006972724976123</v>
       </c>
       <c r="K8" t="n">
-        <v>52.67130150753769</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="L8" t="n">
-        <v>246.8601159786807</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>234.1880104510428</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>374.0000000000004</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,13 +35351,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
@@ -35366,22 +35366,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>130.4306344925853</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>198.871416143795</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K11" t="n">
         <v>177.4460351758794</v>
       </c>
       <c r="L11" t="n">
-        <v>648</v>
+        <v>468.2529823603751</v>
       </c>
       <c r="M11" t="n">
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>643.9166302408599</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P11" t="n">
-        <v>200.3120706125849</v>
+        <v>648.0000000000026</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35609,7 +35609,7 @@
         <v>97.79225094756171</v>
       </c>
       <c r="I13" t="n">
-        <v>163.184183724144</v>
+        <v>158.0039847836788</v>
       </c>
       <c r="J13" t="n">
         <v>329.9707069017971</v>
@@ -35642,7 +35642,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>108.4688411106541</v>
+        <v>113.6490400511193</v>
       </c>
       <c r="U13" t="n">
         <v>170.0757398730831</v>
@@ -35697,13 +35697,13 @@
         <v>177.4460351758794</v>
       </c>
       <c r="L14" t="n">
-        <v>648</v>
+        <v>643.9166302408546</v>
       </c>
       <c r="M14" t="n">
-        <v>643.9166302408598</v>
+        <v>648.0000000000035</v>
       </c>
       <c r="N14" t="n">
-        <v>648</v>
+        <v>648.0000000000035</v>
       </c>
       <c r="O14" t="n">
         <v>164.7897032902292</v>
@@ -35715,7 +35715,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.067033413120291e-11</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -35828,7 +35828,7 @@
         <v>33.88619966292134</v>
       </c>
       <c r="C16" t="n">
-        <v>43.09455441149006</v>
+        <v>48.27475335195533</v>
       </c>
       <c r="D16" t="n">
         <v>35.46378194444452</v>
@@ -35837,7 +35837,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F16" t="n">
-        <v>46.61714403225807</v>
+        <v>41.43694509179277</v>
       </c>
       <c r="G16" t="n">
         <v>76.58186486338801</v>
@@ -35931,22 +35931,22 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K17" t="n">
-        <v>601.2251679293022</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L17" t="n">
-        <v>220.1374974874371</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M17" t="n">
-        <v>648</v>
+        <v>648.0000000000044</v>
       </c>
       <c r="N17" t="n">
-        <v>648</v>
+        <v>648.0000000000044</v>
       </c>
       <c r="O17" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P17" t="n">
-        <v>200.3120706125849</v>
+        <v>624.0912033660007</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -36068,7 +36068,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D19" t="n">
-        <v>30.28358300397924</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E19" t="n">
         <v>40.01909516304346</v>
@@ -36077,7 +36077,7 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G19" t="n">
-        <v>76.58186486338801</v>
+        <v>71.40166592292275</v>
       </c>
       <c r="H19" t="n">
         <v>97.79225094756171</v>
@@ -36171,16 +36171,16 @@
         <v>177.4460351758794</v>
       </c>
       <c r="L20" t="n">
-        <v>220.1374974874373</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M20" t="n">
-        <v>648</v>
+        <v>212.5931175505802</v>
       </c>
       <c r="N20" t="n">
-        <v>47.803414260354</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>164.7897032902292</v>
+        <v>648.0000000000044</v>
       </c>
       <c r="P20" t="n">
         <v>200.3120706125849</v>
@@ -36189,7 +36189,7 @@
         <v>593.6709819069124</v>
       </c>
       <c r="R20" t="n">
-        <v>2.158901564814527e-11</v>
+        <v>3.353187536839584e-11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36311,7 +36311,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F22" t="n">
-        <v>41.43694509179277</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G22" t="n">
         <v>76.58186486338801</v>
@@ -36323,7 +36323,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J22" t="n">
-        <v>329.9707069017971</v>
+        <v>324.7905079613318</v>
       </c>
       <c r="K22" t="n">
         <v>105.178570461152</v>
@@ -36408,19 +36408,19 @@
         <v>177.4460351758794</v>
       </c>
       <c r="L23" t="n">
-        <v>648</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M23" t="n">
-        <v>648</v>
+        <v>624.0912033660087</v>
       </c>
       <c r="N23" t="n">
-        <v>643.9166302408599</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="O23" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P23" t="n">
-        <v>200.3120706125849</v>
+        <v>648.0000000000005</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36545,7 +36545,7 @@
         <v>35.46378194444452</v>
       </c>
       <c r="E25" t="n">
-        <v>40.01909516304346</v>
+        <v>34.83889622257817</v>
       </c>
       <c r="F25" t="n">
         <v>46.61714403225807</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>108.4688411106541</v>
+        <v>113.6490400511193</v>
       </c>
       <c r="U25" t="n">
         <v>170.0757398730831</v>
@@ -36642,16 +36642,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K26" t="n">
+        <v>177.4460351758794</v>
+      </c>
+      <c r="L26" t="n">
+        <v>645.8762262004559</v>
+      </c>
+      <c r="M26" t="n">
         <v>649</v>
       </c>
-      <c r="L26" t="n">
-        <v>220.1374974874373</v>
-      </c>
-      <c r="M26" t="n">
-        <v>649.000000000001</v>
-      </c>
       <c r="N26" t="n">
-        <v>9.513781981984657</v>
+        <v>649</v>
       </c>
       <c r="O26" t="n">
         <v>164.7897032902292</v>
@@ -36660,7 +36660,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q26" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36797,7 +36797,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J28" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K28" t="n">
         <v>105.178570461152</v>
@@ -36830,7 +36830,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U28" t="n">
-        <v>170.0757398730831</v>
+        <v>164.8955409326178</v>
       </c>
       <c r="V28" t="n">
         <v>121.8296897837838</v>
@@ -36879,16 +36879,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K29" t="n">
-        <v>603.1847638888923</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L29" t="n">
-        <v>220.1374974874371</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M29" t="n">
-        <v>649.0000000000028</v>
+        <v>481.0677468061065</v>
       </c>
       <c r="N29" t="n">
-        <v>649.0000000000028</v>
+        <v>649</v>
       </c>
       <c r="O29" t="n">
         <v>164.7897032902292</v>
@@ -36897,7 +36897,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37010,13 +37010,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>33.88619966292134</v>
+        <v>28.7060007224561</v>
       </c>
       <c r="C31" t="n">
         <v>48.27475335195533</v>
       </c>
       <c r="D31" t="n">
-        <v>30.28358300397924</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E31" t="n">
         <v>40.01909516304346</v>
@@ -37113,22 +37113,22 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K32" t="n">
-        <v>177.4460351758794</v>
+        <v>649</v>
       </c>
       <c r="L32" t="n">
-        <v>380.3611929045189</v>
+        <v>649</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>649.0000000000047</v>
+        <v>174.3222613763354</v>
       </c>
       <c r="O32" t="n">
-        <v>649.0000000000047</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P32" t="n">
         <v>200.3120706125849</v>
@@ -37250,7 +37250,7 @@
         <v>33.88619966292134</v>
       </c>
       <c r="C34" t="n">
-        <v>48.27475335195533</v>
+        <v>43.09455441149006</v>
       </c>
       <c r="D34" t="n">
         <v>35.46378194444452</v>
@@ -37304,7 +37304,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U34" t="n">
-        <v>164.8955409326178</v>
+        <v>170.0757398730831</v>
       </c>
       <c r="V34" t="n">
         <v>121.8296897837838</v>
@@ -37353,25 +37353,25 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K35" t="n">
-        <v>177.4460351758794</v>
+        <v>561</v>
       </c>
       <c r="L35" t="n">
+        <v>220.1374974874373</v>
+      </c>
+      <c r="M35" t="n">
         <v>561</v>
       </c>
-      <c r="M35" t="n">
-        <v>77.22148504624087</v>
-      </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>70.05239005703869</v>
       </c>
       <c r="O35" t="n">
+        <v>164.7897032902292</v>
+      </c>
+      <c r="P35" t="n">
         <v>561</v>
       </c>
-      <c r="P35" t="n">
-        <v>200.3120706125849</v>
-      </c>
       <c r="Q35" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37441,7 +37441,7 @@
         <v>276.0650421645042</v>
       </c>
       <c r="N36" t="n">
-        <v>326.5352398450301</v>
+        <v>326.5352398451041</v>
       </c>
       <c r="O36" t="n">
         <v>419.0391822801049</v>
@@ -37487,10 +37487,10 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E37" t="n">
         <v>64.01909516304346</v>
@@ -37505,10 +37505,10 @@
         <v>121.7922509475617</v>
       </c>
       <c r="I37" t="n">
-        <v>153.6860775026446</v>
+        <v>187.184183724144</v>
       </c>
       <c r="J37" t="n">
-        <v>353.9707069017971</v>
+        <v>8.970706901797143</v>
       </c>
       <c r="K37" t="n">
         <v>129.178570461152</v>
@@ -37541,19 +37541,19 @@
         <v>137.6490400511193</v>
       </c>
       <c r="U37" t="n">
-        <v>194.0757398730831</v>
+        <v>100.1209064734635</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>97.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37584,13 +37584,13 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1.091652021304154e-11</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K38" t="n">
-        <v>177.4460351758794</v>
+        <v>430.7403194444537</v>
       </c>
       <c r="L38" t="n">
         <v>220.1374974874373</v>
@@ -37599,7 +37599,7 @@
         <v>561</v>
       </c>
       <c r="N38" t="n">
-        <v>383.9895476824175</v>
+        <v>561</v>
       </c>
       <c r="O38" t="n">
         <v>164.7897032902292</v>
@@ -37611,7 +37611,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.762858818162872e-11</v>
+        <v>5.925495784278169e-11</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -37672,7 +37672,7 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L39" t="n">
-        <v>433.9385745191021</v>
+        <v>433.9385745190838</v>
       </c>
       <c r="M39" t="n">
         <v>276.0650421645042</v>
@@ -37724,10 +37724,10 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>18.77472062589744</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>59.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>64.01909516304346</v>
@@ -37742,10 +37742,10 @@
         <v>121.7922509475617</v>
       </c>
       <c r="I40" t="n">
-        <v>187.184183724144</v>
+        <v>136.0420129463371</v>
       </c>
       <c r="J40" t="n">
-        <v>353.9707069017971</v>
+        <v>8.970706901797143</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -37775,16 +37775,16 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>137.6490400511193</v>
       </c>
       <c r="U40" t="n">
         <v>194.0757398730831</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X40" t="n">
         <v>97.55635456989245</v>
@@ -37830,7 +37830,7 @@
         <v>177.4460351758794</v>
       </c>
       <c r="L41" t="n">
-        <v>220.1374974874373</v>
+        <v>473.4317817560116</v>
       </c>
       <c r="M41" t="n">
         <v>561</v>
@@ -37845,7 +37845,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q41" t="n">
-        <v>253.2942842685745</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37915,7 +37915,7 @@
         <v>276.0650421645042</v>
       </c>
       <c r="N42" t="n">
-        <v>326.5352398451151</v>
+        <v>326.5352398450967</v>
       </c>
       <c r="O42" t="n">
         <v>419.0391822801049</v>
@@ -37967,10 +37967,10 @@
         <v>59.46378194444452</v>
       </c>
       <c r="E43" t="n">
-        <v>64.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>100.581864863388</v>
@@ -37988,7 +37988,7 @@
         <v>129.178570461152</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>14.48250298976183</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -38018,16 +38018,16 @@
         <v>194.0757398730831</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W43" t="n">
-        <v>118.6271901612903</v>
+        <v>71.01355332372603</v>
       </c>
       <c r="X43" t="n">
-        <v>18.08402416003437</v>
+        <v>97.55635456989245</v>
       </c>
       <c r="Y43" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -38070,19 +38070,19 @@
         <v>220.1374974874373</v>
       </c>
       <c r="M44" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>561</v>
+        <v>453.6063548811595</v>
       </c>
       <c r="O44" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P44" t="n">
-        <v>200.3120706125849</v>
+        <v>561</v>
       </c>
       <c r="Q44" t="n">
-        <v>253.2942842685745</v>
+        <v>561</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38146,10 +38146,10 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L45" t="n">
-        <v>433.9385745190245</v>
+        <v>436.150196103404</v>
       </c>
       <c r="M45" t="n">
-        <v>276.0650421645042</v>
+        <v>273.8534205801248</v>
       </c>
       <c r="N45" t="n">
         <v>328.7468614294096</v>
@@ -38207,10 +38207,10 @@
         <v>64.01909516304346</v>
       </c>
       <c r="F46" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>100.581864863388</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>121.7922509475617</v>
@@ -38219,13 +38219,13 @@
         <v>187.184183724144</v>
       </c>
       <c r="J46" t="n">
-        <v>353.9707069017971</v>
+        <v>8.970706901797143</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>75.07555916315641</v>
       </c>
       <c r="L46" t="n">
-        <v>14.48250298976181</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -38249,16 +38249,16 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>137.6490400511193</v>
       </c>
       <c r="U46" t="n">
-        <v>140.5757071470252</v>
+        <v>194.0757398730831</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X46" t="n">
         <v>97.55635456989245</v>
